--- a/scripts/ffn_noise/performance.xlsx
+++ b/scripts/ffn_noise/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="472">
   <si>
     <t>Model</t>
   </si>
@@ -149,7 +154,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0004512065411000089), np.float64(6.292900837660427e-38)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008675887739848397), np.float64(0.673798858214022)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1185430869173045), np.float64(0.2636638839007193)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00289234296845407), np.float64(0.06346135045688442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0033112068240206674), np.float64(0.11082942664579444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012120791154252091), np.float64(0.29912910822754435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0013950900928793254), np.float64(0.5492823706337802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003060184350355541), np.float64(0.0006061890862044585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0063747117152312795), np.float64(0.0003683875101498328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015793459658536388), np.float64(0.00040691569322867427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03137229874669733), np.float64(0.00044666035299128365)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07848695840678241), np.float64(0.0005757556704384568)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.15266695387440118), np.float64(0.00025685958707121273)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.8167225246920354e-05), np.float64(0.9262922309046921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004845738978807847), np.float64(0.3747834817100969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011378091874404803), np.float64(0.07879387750463641)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003065005840602043), np.float64(0.017952839077433887)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0064644588104179265), np.float64(0.012548538891813898)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013021481054110455), np.float64(0.0115997749721876)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.032417857389136016), np.float64(0.012189926042787206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06374297820225451), np.float64(0.011960464888380862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16069856929019646), np.float64(0.012792915825808921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.31195057359340994), np.float64(0.008917020359823488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0002905435747404144), np.float64(0.004947848602368862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.19993031877061e-05), np.float64(0.6242645632397215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00014844515524914113), np.float64(0.34310288808073564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008766825959064785), np.float64(0.004472964886675387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0019364827042933843), np.float64(0.0016324961073928123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0038296171038547364), np.float64(0.0018904640835631858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009436814176726675), np.float64(0.002036331532066949)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.018628011835852786), np.float64(0.00280975337671857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.045330961107533346), np.float64(0.0029865561397941207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09218905263538014), np.float64(0.006174632611431329)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.265480415845552e-05), np.float64(0.4924461501266484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015462460914996838), np.float64(0.25981232929606307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003150999826811677), np.float64(0.06515735016680174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009121628838770591), np.float64(0.007213461912053905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0018275197275993424), np.float64(0.007091970768257994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0034874687847406536), np.float64(0.010140308745546864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008235797554977366), np.float64(0.015102197961575109)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015963149052715668), np.float64(0.018550294462560495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03869427021768641), np.float64(0.019789905804948014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08107062266201964), np.float64(0.028743689846652848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-9.178844327667845e-05), np.float64(0.044858823095439225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.101899846633403e-05), np.float64(0.05942026475456047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0001366164310460829), np.float64(0.00019568856699464504)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00037199203052569463), np.float64(3.5205416560641613e-13)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005905672231600672), np.float64(9.193225967351329e-12)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008719645451947778), np.float64(3.7875710422846194e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014864573565030988), np.float64(9.062188743497502e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002422681097903475), np.float64(0.0009859778625606452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005260097455273431), np.float64(0.006348973219423801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009514101264150364), np.float64(0.007301444057721513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00025175156008836114), np.float64(1.7467857259435017e-24)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00030086087690494115), np.float64(3.055730577273755e-28)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00033705927508033764), np.float64(5.709984891123771e-31)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000451206542294356), np.float64(6.29290156111682e-38)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005555022632875496), np.float64(1.7637651199888002e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006366263794882488), np.float64(2.993512399655061e-38)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007541349911719442), np.float64(2.2424273169047994e-29)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008493031961466496), np.float64(6.884563065359905e-23)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010077136769028772), np.float64(4.8187060849534817e-14)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010865575917834386), np.float64(1.6848236556917923e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.22898588524053076), np.float64(0.01868778203791355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3328716132075153), np.float64(0.010223718732827321)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.21435488512111092), np.float64(0.0033617849495977056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.4333772968952136), np.float64(0.002943154270127206)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05807825583147404), np.float64(0.29420348777975364)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10981447684688658), np.float64(0.3208690451468239)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3218475275019695), np.float64(0.24104672763465787)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6223308024044961), np.float64(0.24520628218870058)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6286498777726832), np.float64(0.21990459024845432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2946875234805093), np.float64(0.3233540677985124)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010283023931919188), np.float64(0.6898457616019305)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01150943768862811), np.float64(0.7350870506030507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012457198546838974), np.float64(0.7576665684794377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02573924206660121), np.float64(0.7494216383447334)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0601324174975905), np.float64(0.7082972367261817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10095561916739693), np.float64(0.7523572901346628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12412562813505737), np.float64(0.875720798349526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.39707846121836), np.float64(0.7940579382016166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05081757425932923), np.float64(0.9891824226278485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8981424302280598), np.float64(0.8928580805686138)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0031034871540428144), np.float64(0.6301310037235912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001894199196796429), np.float64(0.8103270799202651)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0036615161627023855), np.float64(0.7076484063725279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009056067732117293), np.float64(0.6370900209240512)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01719150551584028), np.float64(0.6514653544546563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03530789987177906), np.float64(0.6438167389798858)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03515575643123615), np.float64(0.8508998771845698)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04438707443955302), np.float64(0.9055552271542506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.33032416617927246), np.float64(0.7071154787028125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.0277679411107312), np.float64(0.5845637096097247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0018008012120545771), np.float64(0.7848356323856813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004324939172018541), np.float64(0.6121225575996578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004884368355352409), np.float64(0.6459427925434772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009272836214486033), np.float64(0.6608376984289195)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01840931650374849), np.float64(0.6611917033673451)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.04035738450345614), np.float64(0.6309133513864055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.11570276156543789), np.float64(0.5744088700883037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.20500726546959144), np.float64(0.6146022016218987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3593439199987518), np.float64(0.7072702741690714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1268324640003755), np.float64(0.5845477131013198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005732788759942952), np.float64(0.04394247291078215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0020912708357260727), np.float64(0.2977746465004486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0020817344397992044), np.float64(0.3595706840391747)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0012079293803163374), np.float64(0.699898707260186)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0027222036943626857), np.float64(0.6074414960726483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00415072267394583), np.float64(0.6688824919671832)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00985519738057658), np.float64(0.6670410449261313)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.023042296459872092), np.float64(0.6004641391355621)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.052734127997670494), np.float64(0.6327778098975797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07045708480929898), np.float64(0.722482026364755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0002945312949587627), np.float64(0.842589934452077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0004305352359282521), np.float64(0.7921250326699543)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005680734936917045), np.float64(0.743284492175226)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008675887349376116), np.float64(0.673798873094664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012823944540651196), np.float64(0.5924087468572847)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019839271515961587), np.float64(0.4886349951863635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010588034629572696), np.float64(0.7871310955251813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00043337118436105284), np.float64(0.9315756473493532)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017755124944122422), np.float64(0.8199220897952632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001850705882071964), np.float64(0.857895986929995)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.320301680967029), np.float64(0.020570044125723982)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9207343946874846), np.float64(0.0551129623782495)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.636860541129578), np.float64(0.10204471541180643)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8261686734451991), np.float64(0.40894960982951645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.179847585271287), np.float64(0.029553589113545473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0564499364328594), np.float64(0.0023126469169411135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.43682291204707), np.float64(0.0006183143443521432)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5001602156751517), np.float64(0.0004901567566193088)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.481639799933081), np.float64(0.0005247995326732564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.702711832437223), np.float64(0.00022763545912401123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.625970617187619), np.float64(0.10434153897192096)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7841473164131957), np.float64(0.43318095704585335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.11325603575707772), np.float64(0.9098553941745898)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.5031037359621633), np.float64(0.13319871933014782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1411233294959624), np.float64(0.03255938011797897)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3729485883549604), np.float64(0.017877249527549946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.464751628657049), np.float64(0.013915552710853617)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5058083159157194), np.float64(0.012410606254141225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4871229518917293), np.float64(0.013076632588503395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.625928587426406), np.float64(0.008802988824815366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.430506731235099), np.float64(0.015292010386113079)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.026674039895487), np.float64(0.04302011078460103)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5586032082379537), np.float64(0.11947758204667486)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.20096818203420183), np.float64(0.8407734733348862)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2763555307328196), np.float64(0.20219256370895736)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2257260791618325), np.float64(0.02630469444970461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.803050586508555), np.float64(0.00518208856088562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.870605237167024), np.float64(0.004202723338586751)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.9484333865628334), np.float64(0.00328491790659655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.751139199786064), np.float64(0.006070290763073819)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0515164047714323), np.float64(0.04053500983248624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.668451793625884), np.float64(0.09560922876015215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3314825568433553), np.float64(0.18340165656241356)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19515315523232976), np.float64(0.845321571408265)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.98431598387757), np.float64(0.32525157362736745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7238171440363166), np.float64(0.08511916197097073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1214164382308622), np.float64(0.034187279328835724)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.199606131691355), np.float64(0.028114255656532184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.267032570871104), np.float64(0.023648806830064126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1340314062730354), np.float64(0.03313738350731477)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1306157124179372), np.float64(0.03341889299431513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8715713467052115), np.float64(0.06162306881117645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7244710669624135), np.float64(0.08500107312599631)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2038992014114416), np.float64(0.2289772249933713)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.771655646733605), np.float64(0.44054153552769826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2789808488389094), np.float64(0.7803301230399332)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8781911055010927), np.float64(0.38009820282659923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.7239791041501347), np.float64(0.08508990198581429)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1550647782047703), np.float64(0.0314483153080701)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.403428378270095), np.float64(0.01646405310879983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.503270403565515), np.float64(0.1331557581506462)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4300278687200223), np.float64(0.1530913191752719)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3627768499304402), np.float64(0.1733283463262627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1185430878024372), np.float64(0.2636638835231385)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8828715171825728), np.float64(0.37756539023920926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6614475202053421), np.float64(0.5085118530509627)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.46109027278617537), np.float64(0.6448565607169552)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5108291258880788), np.float64(0.6096087138846396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.15177554877319893), np.float64(0.8794014376950816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.17077559655336932), np.float64(0.864442501477908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004751079080552339), np.float64(0.11916993866583812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006598113248844487), np.float64(0.10961244854133842)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0032496554235131006), np.float64(0.248260459795987)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002529890650122746), np.float64(0.42148465107867245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0028084882368590316), np.float64(3.794385567208311e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005916609041657631), np.float64(1.8476617158794153e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.015277566799547334), np.float64(0.00015787268017919732)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.031019976855717273), np.float64(0.00039792868732942696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07790183464113692), np.float64(0.0005538335508056253)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1510774911378552), np.float64(0.0002299174696377404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001619641242324636), np.float64(0.5971313595693402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003146198670965096), np.float64(0.40438913000258314)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008716960331797763), np.float64(0.039895462989716975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0028315744050371513), np.float64(0.011459705872221376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005199577229341013), np.float64(0.0006926550453458893)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009917171730399485), np.float64(0.0001517174720745416)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024325804725451632), np.float64(0.00021149766587197927)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04766455472393641), np.float64(0.00022698964776463474)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12074846562226237), np.float64(0.00029346537841155017)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.24923583396323115), np.float64(0.0006419849011523128)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00029935206021755107), np.float64(0.0037401098564455036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-9.249817914062682e-05), np.float64(0.4650227198611261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011814177919955829), np.float64(0.45004704398115375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008536846911672328), np.float64(0.005105315886567056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001886119191049455), np.float64(0.0014561865422998315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0036963486711429146), np.float64(0.0013104165297966215)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008904876125573585), np.float64(0.0008341552882570156)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017291729593533395), np.float64(0.0007806042050890489)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04173139299969124), np.float64(0.0007183980402070772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08422166211406815), np.float64(0.0016437554997193635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.984676926271995e-05), np.float64(0.44473397922047353)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00014045952890192047), np.float64(0.3001539055528817)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003004390571208308), np.float64(0.06697289180558298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008829733556374172), np.float64(0.005991870976690288)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0017721420662983381), np.float64(0.005565627449670872)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0034488817589784396), np.float64(0.009845489949480837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00795666711459929), np.float64(0.01216151300015315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01558680738299381), np.float64(0.016062525634259854)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03770542898409677), np.float64(0.017243800281666877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07780446695845794), np.float64(0.023539306805505898)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00017671198419527627), np.float64(0.04630320199767791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001085860465350683), np.float64(0.3646299562062946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.09891875553409e-05), np.float64(0.6235988807353946)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00035673262212031014), np.float64(1.2618906925194828e-12)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005747762532241029), np.float64(6.05630982832081e-12)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000856827516335262), np.float64(1.7779733303638014e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014605274063515244), np.float64(5.657393170304333e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0023677729634479375), np.float64(0.0007470399419407104)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005079412588129417), np.float64(0.0048400674186395275)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009166692831691605), np.float64(0.005733419564507101)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002459526534841996), np.float64(1.3035579444231453e-23)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002961530625581605), np.float64(1.732594202693461e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00033341211121845247), np.float64(2.1574829305265484e-30)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00044988091382513616), np.float64(1.101261317180331e-37)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005532650432671116), np.float64(2.9519283832935216e-41)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000633488827369002), np.float64(4.934647463395592e-38)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007507745561406196), np.float64(2.889160424156642e-29)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0008434099843083122), np.float64(1.1726585033502347e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010032630040908946), np.float64(6.849162358743857e-14)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.001075282770311747), np.float64(2.5221665930190584e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3614811749661047), np.float64(0.057834558070532664)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.6609460085816686), np.float64(0.010260687361470608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.49264658573518905), np.float64(0.00517632260709905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5689246354299211), np.float64(0.003823546159097782)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04084246495797676), np.float64(0.3337984567074585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07548754621187893), np.float64(0.37546639332803683)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.27760022342862617), np.float64(0.26450014018496487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5973508662203829), np.float64(0.2553540181402803)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4638035883627336), np.float64(0.26598695765298697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.246036653227779), np.float64(0.32582876327827115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00478049414643634), np.float64(0.8028072341965986)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003292604937275691), np.float64(0.8886278860380731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005233712171244722), np.float64(0.8431269174104246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.019914865940292098), np.float64(0.7750567590555208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01926403264623126), np.float64(0.8393897547025259)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0034479273299067932), np.float64(0.9830312169942247)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009532097327121552), np.float64(0.9811484188779601)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.10721152112946067), np.float64(0.8896779547182458)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3426693024170877), np.float64(0.8596103001101795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2768297051063431), np.float64(0.9459671883570772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0028619534464821715), np.float64(0.6565726730532585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002597911531671356), np.float64(0.7417556433381883)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005241006116322866), np.float64(0.5907907057972014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009146940467924554), np.float64(0.629871732029281)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0180598998772365), np.float64(0.6228212657111367)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03532164768805556), np.float64(0.6200818686596961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04518588695376681), np.float64(0.78137052649535)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07029765580813453), np.float64(0.8195369821021846)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3583365266649965), np.float64(0.6153430675998984)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8331332600028308), np.float64(0.5763065688949697)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019602557798772294), np.float64(0.7635117949663427)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003958672266405115), np.float64(0.6386294974473607)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004938034546045473), np.float64(0.6286471196417739)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009270814477051094), np.float64(0.6433406618820499)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.018173699737562117), np.float64(0.6463194566302237)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03904652429859727), np.float64(0.6366226047648325)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.10182639992727975), np.float64(0.5977406313618752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.19634705578658984), np.float64(0.6127776427005401)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.35497542116016423), np.float64(0.6963436602929557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.079964248927995), np.float64(0.5716567488817513)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003476286946848442), np.float64(0.5281004911160483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0033643563193275073), np.float64(0.6508643843803326)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007986361405615044), np.float64(0.12440619735644254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013956649523828432), np.float64(0.6503171720017538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0024510689521483036), np.float64(0.631097349227975)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004026649845751134), np.float64(0.6653646018296081)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009046444380257378), np.float64(0.6790032531198193)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0216222266469141), np.float64(0.6076785349456219)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.049453637752699876), np.float64(0.6306698140369547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06371811124579896), np.float64(0.732368817716304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0002727340896384575), np.float64(0.8536782291099557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00044350729589951837), np.float64(0.7859501462965114)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0005609366640426244), np.float64(0.7463995751803361)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0008237673212083785), np.float64(0.6895303678610238)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012981305227740736), np.float64(0.5878401371076024)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.002010892559695691), np.float64(0.4811662462939696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001209181564013315), np.float64(0.7567391460874401)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003976088667968008), np.float64(0.9368561726028463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015024998123008546), np.float64(0.8474248796838085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0014885305889519428), np.float64(0.8858779748414564)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.782289322788775), np.float64(0.07507334930718175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.69503291873076), np.float64(0.09045022632290349)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3412691062318998), np.float64(0.18020582502788904)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9355647304677118), np.float64(0.3497737845619447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3072839841450814), np.float64(0.02128817079879489)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5283422302740526), np.float64(0.00044151747000784465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6585593809703085), np.float64(0.000269905501470171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.527124309905266), np.float64(0.0004435226008611144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.487816687780775), np.float64(0.0005129992005404482)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.7302759700460904), np.float64(0.0002044911271275753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.98384807005383), np.float64(0.04760707153946442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1666241383958054), np.float64(0.24370260256947848)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.24663338446571267), np.float64(0.805253920466597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.505462549467226), np.float64(0.1325916978847402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.6764908706505666), np.float64(0.007588850845497871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.411169478654786), np.float64(0.0006786114158153625)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6029405692235255), np.float64(0.00033366632029082147)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6568759230166368), np.float64(0.0002716546339258581)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.6094626738920588), np.float64(0.00032551774771362885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.423955049613043), np.float64(0.0006479062066537382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.456211813128265), np.float64(0.014248137863453225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.091720141911474), np.float64(0.03677177704283595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6164821825231022), np.float64(0.10637613712213312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.22957167310060972), np.float64(0.8184820810001632)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.2629975392187611), np.float64(0.20695039215646957)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2526024288633635), np.float64(0.02454886228636452)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0206129213497452), np.float64(0.002601236458576171)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2168613994484883), np.float64(0.0013470425179785035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.357845887510731), np.float64(0.0008218652048302864)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.158909979526603), np.float64(0.0016418648567213792)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0580487090010124), np.float64(0.039902170521146176)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6648385389019624), np.float64(0.09632838120897909)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3701852868566373), np.float64(0.17100545493315208)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.24158979440433723), np.float64(0.8091586525769815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.9460319492365052), np.float64(0.34441199447170473)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.724746164707669), np.float64(0.08495143420863654)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1891781075443926), np.float64(0.028866170290129382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.246560635301414), np.float64(0.02493445175636075)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3124863783499787), np.float64(0.020998595400491635)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2059398846503937), np.float64(0.027665863569475906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.2315550633059154), np.float64(0.025914917477151047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0920261164402314), np.float64(0.036744320467748656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8684972514179508), np.float64(0.062050482032686705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2399381072271292), np.float64(0.21535429583460802)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7883965022828083), np.float64(0.4306935105083163)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2946782930483199), np.float64(0.7683145056541264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8577682747310122), np.float64(0.3912719852144123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6756255785669651), np.float64(0.09419418365460645)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1949819457368975), np.float64(0.02844557080488472)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.458794389748542), np.float64(0.014146825364250626)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5242158199120865), np.float64(0.12784178241593813)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4395754062638921), np.float64(0.15037059404281153)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3631828286582142), np.float64(0.17320044421604336)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.1168918276060817), np.float64(0.26436892995994554)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9090427494060603), np.float64(0.36359563978539605)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6745107875267418), np.float64(0.5001774422950264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4229924062074944), np.float64(0.6724121145879801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5833478469733728), np.float64(0.5598201501683551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.09081230224411525), np.float64(0.9276639939868125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2800707438560806), np.float64(0.7794941252435965)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1506,10 +2792,6169 @@
         <v>44</v>
       </c>
       <c r="V12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W12" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0009256656994917029</v>
+      </c>
+      <c r="D2">
+        <v>-0.002641567029058933</v>
+      </c>
+      <c r="E2">
+        <v>0.04453058540821075</v>
+      </c>
+      <c r="F2">
+        <v>0.0008037119987420738</v>
+      </c>
+      <c r="G2">
+        <v>0.0009139182511717081</v>
+      </c>
+      <c r="H2">
+        <v>1.000379938883115</v>
+      </c>
+      <c r="I2">
+        <v>0.04913031796078562</v>
+      </c>
+      <c r="J2">
+        <v>-0.05932028591632843</v>
+      </c>
+      <c r="K2">
+        <v>-0.99982750415802</v>
+      </c>
+      <c r="L2">
+        <v>2.548768281936646</v>
+      </c>
+      <c r="M2">
+        <v>-3.395276784896851</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.001232314152733618</v>
+      </c>
+      <c r="D3">
+        <v>-0.002949027577415109</v>
+      </c>
+      <c r="E3">
+        <v>0.05939670652151108</v>
+      </c>
+      <c r="F3">
+        <v>0.0009084125049412251</v>
+      </c>
+      <c r="G3">
+        <v>0.0009561735787428916</v>
+      </c>
+      <c r="H3">
+        <v>1.000610062405822</v>
+      </c>
+      <c r="I3">
+        <v>0.04904264420299137</v>
+      </c>
+      <c r="J3">
+        <v>-0.0496496818959713</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999371767044067</v>
+      </c>
+      <c r="L3">
+        <v>3.399650812149048</v>
+      </c>
+      <c r="M3">
+        <v>-2.841766595840454</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001537340265993141</v>
+      </c>
+      <c r="D4">
+        <v>-0.0009874382521957159</v>
+      </c>
+      <c r="E4">
+        <v>0.0334501676261425</v>
+      </c>
+      <c r="F4">
+        <v>0.0009993981802836061</v>
+      </c>
+      <c r="G4">
+        <v>0.001033458160236478</v>
+      </c>
+      <c r="H4">
+        <v>1.000710227365641</v>
+      </c>
+      <c r="I4">
+        <v>0.04911113462467665</v>
+      </c>
+      <c r="J4">
+        <v>-0.02951968088746071</v>
+      </c>
+      <c r="K4">
+        <v>-0.9606931209564209</v>
+      </c>
+      <c r="L4">
+        <v>1.914565563201904</v>
+      </c>
+      <c r="M4">
+        <v>-1.689598798751831</v>
+      </c>
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.003041009193777836</v>
+      </c>
+      <c r="D5">
+        <v>-0.0009805408772081137</v>
+      </c>
+      <c r="E5">
+        <v>0.06680423021316528</v>
+      </c>
+      <c r="F5">
+        <v>0.001279438612982631</v>
+      </c>
+      <c r="G5">
+        <v>0.001246839412488043</v>
+      </c>
+      <c r="H5">
+        <v>1.000796997182392</v>
+      </c>
+      <c r="I5">
+        <v>0.04918299809363783</v>
+      </c>
+      <c r="J5">
+        <v>-0.01467782631516457</v>
+      </c>
+      <c r="K5">
+        <v>-0.959799587726593</v>
+      </c>
+      <c r="L5">
+        <v>3.823630332946777</v>
+      </c>
+      <c r="M5">
+        <v>-0.8401052355766296</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" t="s">
+        <v>174</v>
+      </c>
+      <c r="P5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.006004654623458584</v>
+      </c>
+      <c r="D6">
+        <v>0.003110060701146722</v>
+      </c>
+      <c r="E6">
+        <v>0.02539124339818954</v>
+      </c>
+      <c r="F6">
+        <v>0.001542523037642241</v>
+      </c>
+      <c r="G6">
+        <v>0.001455603865906596</v>
+      </c>
+      <c r="H6">
+        <v>1.000919424671879</v>
+      </c>
+      <c r="I6">
+        <v>0.04930603208605366</v>
+      </c>
+      <c r="J6">
+        <v>0.122485563158989</v>
+      </c>
+      <c r="K6">
+        <v>26178.107421875</v>
+      </c>
+      <c r="L6">
+        <v>1.453302145004272</v>
+      </c>
+      <c r="M6">
+        <v>7.010626792907715</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.0118966503038599</v>
+      </c>
+      <c r="D7">
+        <v>0.00646424014121294</v>
+      </c>
+      <c r="E7">
+        <v>0.05090843513607979</v>
+      </c>
+      <c r="F7">
+        <v>0.001776542863808572</v>
+      </c>
+      <c r="G7">
+        <v>0.001754417316988111</v>
+      </c>
+      <c r="H7">
+        <v>1.001187971304411</v>
+      </c>
+      <c r="I7">
+        <v>0.04902915954442729</v>
+      </c>
+      <c r="J7">
+        <v>0.1269777864217758</v>
+      </c>
+      <c r="K7">
+        <v>1470263168</v>
+      </c>
+      <c r="L7">
+        <v>2.91381311416626</v>
+      </c>
+      <c r="M7">
+        <v>7.267745018005371</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02943149548903267</v>
+      </c>
+      <c r="D8">
+        <v>0.01601691730320454</v>
+      </c>
+      <c r="E8">
+        <v>0.1271447390317917</v>
+      </c>
+      <c r="F8">
+        <v>0.00205272575840354</v>
+      </c>
+      <c r="G8">
+        <v>0.00214000977575779</v>
+      </c>
+      <c r="H8">
+        <v>1.0015405077113</v>
+      </c>
+      <c r="I8">
+        <v>0.04965469487407401</v>
+      </c>
+      <c r="J8">
+        <v>0.1259738951921463</v>
+      </c>
+      <c r="K8">
+        <v>4.050764936638206E+22</v>
+      </c>
+      <c r="L8">
+        <v>7.277300834655762</v>
+      </c>
+      <c r="M8">
+        <v>7.210286140441895</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O8" t="s">
+        <v>177</v>
+      </c>
+      <c r="P8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.05865506170336239</v>
+      </c>
+      <c r="D9">
+        <v>0.03179972618818283</v>
+      </c>
+      <c r="E9">
+        <v>0.2543644607067108</v>
+      </c>
+      <c r="F9">
+        <v>0.00222553638741374</v>
+      </c>
+      <c r="G9">
+        <v>0.002398994052782655</v>
+      </c>
+      <c r="H9">
+        <v>1.001843243623203</v>
+      </c>
+      <c r="I9">
+        <v>0.05018541637522048</v>
+      </c>
+      <c r="J9">
+        <v>0.1250163912773132</v>
+      </c>
+      <c r="K9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9">
+        <v>14.55889320373535</v>
+      </c>
+      <c r="M9">
+        <v>7.155481815338135</v>
+      </c>
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1476463516735807</v>
+      </c>
+      <c r="D10">
+        <v>0.0796857550740242</v>
+      </c>
+      <c r="E10">
+        <v>0.6490591168403625</v>
+      </c>
+      <c r="F10">
+        <v>0.002343948464840651</v>
+      </c>
+      <c r="G10">
+        <v>0.002675158670172095</v>
+      </c>
+      <c r="H10">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I10">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J10">
+        <v>0.122771181166172</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>37.14977645874023</v>
+      </c>
+      <c r="M10">
+        <v>7.026974201202393</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.2868880552611597</v>
+      </c>
+      <c r="D11">
+        <v>0.154563695192337</v>
+      </c>
+      <c r="E11">
+        <v>1.187989115715027</v>
+      </c>
+      <c r="F11">
+        <v>0.002443826757371426</v>
+      </c>
+      <c r="G11">
+        <v>0.002929799258708954</v>
+      </c>
+      <c r="H11">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I11">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J11">
+        <v>0.1301053166389465</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>67.99616241455078</v>
+      </c>
+      <c r="M11">
+        <v>7.44675350189209</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+      <c r="O11" t="s">
+        <v>180</v>
+      </c>
+      <c r="P11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001769786356084436</v>
+      </c>
+      <c r="D12">
+        <v>-2.691992267500609E-05</v>
+      </c>
+      <c r="E12">
+        <v>0.01176255103200674</v>
+      </c>
+      <c r="F12">
+        <v>0.0008055421058088541</v>
+      </c>
+      <c r="G12">
+        <v>0.0009082467295229435</v>
+      </c>
+      <c r="H12">
+        <v>1.00036856587502</v>
+      </c>
+      <c r="I12">
+        <v>0.04917026984624779</v>
+      </c>
+      <c r="J12">
+        <v>-0.00228861253708601</v>
+      </c>
+      <c r="K12">
+        <v>-0.08447802066802979</v>
+      </c>
+      <c r="L12">
+        <v>0.6732454895973206</v>
+      </c>
+      <c r="M12">
+        <v>-0.1309918314218521</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+      <c r="O12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.002357227869257947</v>
+      </c>
+      <c r="D13">
+        <v>0.0004973030299879611</v>
+      </c>
+      <c r="E13">
+        <v>0.01556098833680153</v>
+      </c>
+      <c r="F13">
+        <v>0.0009118986199609935</v>
+      </c>
+      <c r="G13">
+        <v>0.0009538953891023993</v>
+      </c>
+      <c r="H13">
+        <v>1.00053858220103</v>
+      </c>
+      <c r="I13">
+        <v>0.04913154629504497</v>
+      </c>
+      <c r="J13">
+        <v>0.03195831924676895</v>
+      </c>
+      <c r="K13">
+        <v>4.098185062408447</v>
+      </c>
+      <c r="L13">
+        <v>0.8906542062759399</v>
+      </c>
+      <c r="M13">
+        <v>1.829177618026733</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O13" t="s">
+        <v>182</v>
+      </c>
+      <c r="P13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.002942108509421238</v>
+      </c>
+      <c r="D14">
+        <v>0.001150949159637094</v>
+      </c>
+      <c r="E14">
+        <v>0.01844020746648312</v>
+      </c>
+      <c r="F14">
+        <v>0.001021204865537584</v>
+      </c>
+      <c r="G14">
+        <v>0.001034669810906053</v>
+      </c>
+      <c r="H14">
+        <v>1.000605522801575</v>
+      </c>
+      <c r="I14">
+        <v>0.04917529946344398</v>
+      </c>
+      <c r="J14">
+        <v>0.06241519749164581</v>
+      </c>
+      <c r="K14">
+        <v>42.31051254272461</v>
+      </c>
+      <c r="L14">
+        <v>1.055450201034546</v>
+      </c>
+      <c r="M14">
+        <v>3.572418212890625</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+      <c r="O14" t="s">
+        <v>183</v>
+      </c>
+      <c r="P14" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.005847942004017251</v>
+      </c>
+      <c r="D15">
+        <v>0.00309038395062089</v>
+      </c>
+      <c r="E15">
+        <v>0.03687614947557449</v>
+      </c>
+      <c r="F15">
+        <v>0.001300806179642677</v>
+      </c>
+      <c r="G15">
+        <v>0.0012516820570454</v>
+      </c>
+      <c r="H15">
+        <v>1.00068646452249</v>
+      </c>
+      <c r="I15">
+        <v>0.04928026258939175</v>
+      </c>
+      <c r="J15">
+        <v>0.0838044136762619</v>
+      </c>
+      <c r="K15">
+        <v>24549.283203125</v>
+      </c>
+      <c r="L15">
+        <v>2.110656261444092</v>
+      </c>
+      <c r="M15">
+        <v>4.796658992767334</v>
+      </c>
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+      <c r="O15" t="s">
+        <v>184</v>
+      </c>
+      <c r="P15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.01160873419520036</v>
+      </c>
+      <c r="D16">
+        <v>0.006517515052109957</v>
+      </c>
+      <c r="E16">
+        <v>0.07374969124794006</v>
+      </c>
+      <c r="F16">
+        <v>0.001572426757775247</v>
+      </c>
+      <c r="G16">
+        <v>0.00149068224709481</v>
+      </c>
+      <c r="H16">
+        <v>1.000841729237631</v>
+      </c>
+      <c r="I16">
+        <v>0.04934886419979641</v>
+      </c>
+      <c r="J16">
+        <v>0.08837345242500305</v>
+      </c>
+      <c r="K16">
+        <v>1748716928</v>
+      </c>
+      <c r="L16">
+        <v>4.221163272857666</v>
+      </c>
+      <c r="M16">
+        <v>5.058174133300781</v>
+      </c>
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+      <c r="O16" t="s">
+        <v>185</v>
+      </c>
+      <c r="P16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.02305067190679751</v>
+      </c>
+      <c r="D17">
+        <v>0.0131083307787776</v>
+      </c>
+      <c r="E17">
+        <v>0.146922841668129</v>
+      </c>
+      <c r="F17">
+        <v>0.001798146520741284</v>
+      </c>
+      <c r="G17">
+        <v>0.001797159551642835</v>
+      </c>
+      <c r="H17">
+        <v>1.001139624912782</v>
+      </c>
+      <c r="I17">
+        <v>0.04906989995502023</v>
+      </c>
+      <c r="J17">
+        <v>0.08921914547681808</v>
+      </c>
+      <c r="K17">
+        <v>3.378650248330084E+18</v>
+      </c>
+      <c r="L17">
+        <v>8.409327507019043</v>
+      </c>
+      <c r="M17">
+        <v>5.106578350067139</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+      <c r="O17" t="s">
+        <v>186</v>
+      </c>
+      <c r="P17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.05735601829133713</v>
+      </c>
+      <c r="D18">
+        <v>0.03250858560204506</v>
+      </c>
+      <c r="E18">
+        <v>0.3684748113155365</v>
+      </c>
+      <c r="F18">
+        <v>0.00205905013717711</v>
+      </c>
+      <c r="G18">
+        <v>0.002183117903769016</v>
+      </c>
+      <c r="H18">
+        <v>1.001552102764744</v>
+      </c>
+      <c r="I18">
+        <v>0.04961785715302058</v>
+      </c>
+      <c r="J18">
+        <v>0.08822471648454666</v>
+      </c>
+      <c r="K18" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18">
+        <v>21.09015274047852</v>
+      </c>
+      <c r="M18">
+        <v>5.049660682678223</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O18" t="s">
+        <v>187</v>
+      </c>
+      <c r="P18" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.113232595768443</v>
+      </c>
+      <c r="D19">
+        <v>0.06402042508125305</v>
+      </c>
+      <c r="E19">
+        <v>0.7226994633674622</v>
+      </c>
+      <c r="F19">
+        <v>0.002197968307882547</v>
+      </c>
+      <c r="G19">
+        <v>0.002409211127087474</v>
+      </c>
+      <c r="H19">
+        <v>1.00192085169799</v>
+      </c>
+      <c r="I19">
+        <v>0.05009964352345458</v>
+      </c>
+      <c r="J19">
+        <v>0.08858513087034225</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>41.36468124389648</v>
+      </c>
+      <c r="M19">
+        <v>5.070289611816406</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" t="s">
+        <v>188</v>
+      </c>
+      <c r="P19" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.2851451267895235</v>
+      </c>
+      <c r="D20">
+        <v>0.1607404500246048</v>
+      </c>
+      <c r="E20">
+        <v>1.838888883590698</v>
+      </c>
+      <c r="F20">
+        <v>0.002349025569856167</v>
+      </c>
+      <c r="G20">
+        <v>0.002698393538594246</v>
+      </c>
+      <c r="H20">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I20">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J20">
+        <v>0.08741172403097153</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>105.2512893676758</v>
+      </c>
+      <c r="M20">
+        <v>5.003128051757812</v>
+      </c>
+      <c r="N20" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.5533698135528546</v>
+      </c>
+      <c r="D21">
+        <v>0.3127909600734711</v>
+      </c>
+      <c r="E21">
+        <v>3.396656274795532</v>
+      </c>
+      <c r="F21">
+        <v>0.002449471736326814</v>
+      </c>
+      <c r="G21">
+        <v>0.002961830934509635</v>
+      </c>
+      <c r="H21">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I21">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J21">
+        <v>0.09208790212869644</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>194.4122161865234</v>
+      </c>
+      <c r="M21">
+        <v>5.270775318145752</v>
+      </c>
+      <c r="N21" t="s">
+        <v>130</v>
+      </c>
+      <c r="O21" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0005678498750447075</v>
+      </c>
+      <c r="D22">
+        <v>-0.0002871634787879884</v>
+      </c>
+      <c r="E22">
+        <v>0.002940496196970344</v>
+      </c>
+      <c r="F22">
+        <v>0.0008248304948210716</v>
+      </c>
+      <c r="G22">
+        <v>0.000922066334169358</v>
+      </c>
+      <c r="H22">
+        <v>1.000233123695376</v>
+      </c>
+      <c r="I22">
+        <v>0.0492651336360596</v>
+      </c>
+      <c r="J22">
+        <v>-0.09765817224979401</v>
+      </c>
+      <c r="K22">
+        <v>-0.6097317934036255</v>
+      </c>
+      <c r="L22">
+        <v>0.1683032661676407</v>
+      </c>
+      <c r="M22">
+        <v>-5.589597225189209</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+      <c r="O22" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0007536162197851609</v>
+      </c>
+      <c r="D23">
+        <v>-5.991408033878542E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.003608193481341004</v>
+      </c>
+      <c r="F23">
+        <v>0.000942331796977669</v>
+      </c>
+      <c r="G23">
+        <v>0.000979610369540751</v>
+      </c>
+      <c r="H23">
+        <v>1.000416637376212</v>
+      </c>
+      <c r="I23">
+        <v>0.04919605256706662</v>
+      </c>
+      <c r="J23">
+        <v>-0.01660500839352608</v>
+      </c>
+      <c r="K23">
+        <v>-0.1781907677650452</v>
+      </c>
+      <c r="L23">
+        <v>0.206519827246666</v>
+      </c>
+      <c r="M23">
+        <v>-0.9504100680351257</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+      <c r="O23" t="s">
+        <v>192</v>
+      </c>
+      <c r="P23" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0009366197151148323</v>
+      </c>
+      <c r="D24">
+        <v>0.0001523076061857864</v>
+      </c>
+      <c r="E24">
+        <v>0.004463620018213987</v>
+      </c>
+      <c r="F24">
+        <v>0.001057363348081708</v>
+      </c>
+      <c r="G24">
+        <v>0.001058273832313716</v>
+      </c>
+      <c r="H24">
+        <v>1.000461596171587</v>
+      </c>
+      <c r="I24">
+        <v>0.04926897788660002</v>
+      </c>
+      <c r="J24">
+        <v>0.03412199020385742</v>
+      </c>
+      <c r="K24">
+        <v>0.6471703052520752</v>
+      </c>
+      <c r="L24">
+        <v>0.2554813325405121</v>
+      </c>
+      <c r="M24">
+        <v>1.953018188476562</v>
+      </c>
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+      <c r="O24" t="s">
+        <v>193</v>
+      </c>
+      <c r="P24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001826095512920121</v>
+      </c>
+      <c r="D25">
+        <v>0.0008858583169057965</v>
+      </c>
+      <c r="E25">
+        <v>0.008774011395871639</v>
+      </c>
+      <c r="F25">
+        <v>0.001335557084530592</v>
+      </c>
+      <c r="G25">
+        <v>0.001279076677747071</v>
+      </c>
+      <c r="H25">
+        <v>1.000577809020304</v>
+      </c>
+      <c r="I25">
+        <v>0.0494088742668091</v>
+      </c>
+      <c r="J25">
+        <v>0.1009638905525208</v>
+      </c>
+      <c r="K25">
+        <v>17.18761825561523</v>
+      </c>
+      <c r="L25">
+        <v>0.5021923780441284</v>
+      </c>
+      <c r="M25">
+        <v>5.778804779052734</v>
+      </c>
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O25" t="s">
+        <v>194</v>
+      </c>
+      <c r="P25" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.003555680894793088</v>
+      </c>
+      <c r="D26">
+        <v>0.001951952697709203</v>
+      </c>
+      <c r="E26">
+        <v>0.0174875371158123</v>
+      </c>
+      <c r="F26">
+        <v>0.001599243027158082</v>
+      </c>
+      <c r="G26">
+        <v>0.001549069536849856</v>
+      </c>
+      <c r="H26">
+        <v>1.000739365250885</v>
+      </c>
+      <c r="I26">
+        <v>0.04945673093612767</v>
+      </c>
+      <c r="J26">
+        <v>0.1116196438670158</v>
+      </c>
+      <c r="K26">
+        <v>593.8441772460938</v>
+      </c>
+      <c r="L26">
+        <v>1.000922799110413</v>
+      </c>
+      <c r="M26">
+        <v>6.38870096206665</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
+        <v>195</v>
+      </c>
+      <c r="P26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.006971327378925988</v>
+      </c>
+      <c r="D27">
+        <v>0.003860571654513478</v>
+      </c>
+      <c r="E27">
+        <v>0.03506937995553017</v>
+      </c>
+      <c r="F27">
+        <v>0.001845675404183567</v>
+      </c>
+      <c r="G27">
+        <v>0.001837755204178393</v>
+      </c>
+      <c r="H27">
+        <v>1.001065208041409</v>
+      </c>
+      <c r="I27">
+        <v>0.04917730090153912</v>
+      </c>
+      <c r="J27">
+        <v>0.1100838333368301</v>
+      </c>
+      <c r="K27">
+        <v>303442.8125</v>
+      </c>
+      <c r="L27">
+        <v>2.007243394851685</v>
+      </c>
+      <c r="M27">
+        <v>6.300796985626221</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+      <c r="O27" t="s">
+        <v>196</v>
+      </c>
+      <c r="P27" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.01709369767596338</v>
+      </c>
+      <c r="D28">
+        <v>0.009464763104915619</v>
+      </c>
+      <c r="E28">
+        <v>0.08705409616231918</v>
+      </c>
+      <c r="F28">
+        <v>0.002089670393615961</v>
+      </c>
+      <c r="G28">
+        <v>0.00220404751598835</v>
+      </c>
+      <c r="H28">
+        <v>1.001571681003996</v>
+      </c>
+      <c r="I28">
+        <v>0.04958796772445206</v>
+      </c>
+      <c r="J28">
+        <v>0.1087227761745453</v>
+      </c>
+      <c r="K28">
+        <v>25270931161088</v>
+      </c>
+      <c r="L28">
+        <v>4.982658863067627</v>
+      </c>
+      <c r="M28">
+        <v>6.22289514541626</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" t="s">
+        <v>197</v>
+      </c>
+      <c r="P28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.03417849919240452</v>
+      </c>
+      <c r="D29">
+        <v>0.01866259798407555</v>
+      </c>
+      <c r="E29">
+        <v>0.1774705052375793</v>
+      </c>
+      <c r="F29">
+        <v>0.002197374822571874</v>
+      </c>
+      <c r="G29">
+        <v>0.002427200553938746</v>
+      </c>
+      <c r="H29">
+        <v>1.001894243215206</v>
+      </c>
+      <c r="I29">
+        <v>0.05008331515582814</v>
+      </c>
+      <c r="J29">
+        <v>0.1051588729023933</v>
+      </c>
+      <c r="K29">
+        <v>2.029666842444388E+26</v>
+      </c>
+      <c r="L29">
+        <v>10.15776443481445</v>
+      </c>
+      <c r="M29">
+        <v>6.018909931182861</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+      <c r="O29" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.08431689331765366</v>
+      </c>
+      <c r="D30">
+        <v>0.0455801822245121</v>
+      </c>
+      <c r="E30">
+        <v>0.4347059428691864</v>
+      </c>
+      <c r="F30">
+        <v>0.002331178402528167</v>
+      </c>
+      <c r="G30">
+        <v>0.00269700400531292</v>
+      </c>
+      <c r="H30">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I30">
+        <v>0.05575669690240725</v>
+      </c>
+      <c r="J30">
+        <v>0.1048529073596001</v>
+      </c>
+      <c r="K30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30">
+        <v>24.8809814453125</v>
+      </c>
+      <c r="M30">
+        <v>6.001397609710693</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>199</v>
+      </c>
+      <c r="P30" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.1734484100382089</v>
+      </c>
+      <c r="D31">
+        <v>0.09307917952537537</v>
+      </c>
+      <c r="E31">
+        <v>0.9588181376457214</v>
+      </c>
+      <c r="F31">
+        <v>0.002424088306725025</v>
+      </c>
+      <c r="G31">
+        <v>0.002974679693579674</v>
+      </c>
+      <c r="H31">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I31">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J31">
+        <v>0.09707698971033096</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>54.87925338745117</v>
+      </c>
+      <c r="M31">
+        <v>5.556332588195801</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+      <c r="O31" t="s">
+        <v>200</v>
+      </c>
+      <c r="P31" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0005052105728058137</v>
+      </c>
+      <c r="D32">
+        <v>-7.462948269676417E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003017105394974351</v>
+      </c>
+      <c r="F32">
+        <v>0.0008695712895132601</v>
+      </c>
+      <c r="G32">
+        <v>0.0009404662996530533</v>
+      </c>
+      <c r="H32">
+        <v>1.000121511583036</v>
+      </c>
+      <c r="I32">
+        <v>0.04935711853077204</v>
+      </c>
+      <c r="J32">
+        <v>-0.0247354581952095</v>
+      </c>
+      <c r="K32">
+        <v>-0.2168889045715332</v>
+      </c>
+      <c r="L32">
+        <v>0.1726880967617035</v>
+      </c>
+      <c r="M32">
+        <v>-1.415767312049866</v>
+      </c>
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+      <c r="O32" t="s">
+        <v>201</v>
+      </c>
+      <c r="P32" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0006680531124997444</v>
+      </c>
+      <c r="D33">
+        <v>0.000149791085277684</v>
+      </c>
+      <c r="E33">
+        <v>0.003910607658326626</v>
+      </c>
+      <c r="F33">
+        <v>0.0009976314613595605</v>
+      </c>
+      <c r="G33">
+        <v>0.001010060892440379</v>
+      </c>
+      <c r="H33">
+        <v>1.000231243418048</v>
+      </c>
+      <c r="I33">
+        <v>0.04937160481000808</v>
+      </c>
+      <c r="J33">
+        <v>0.03830378875136375</v>
+      </c>
+      <c r="K33">
+        <v>0.6337189674377441</v>
+      </c>
+      <c r="L33">
+        <v>0.223828911781311</v>
+      </c>
+      <c r="M33">
+        <v>2.192368984222412</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+      <c r="O33" t="s">
+        <v>202</v>
+      </c>
+      <c r="P33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0008273644933293727</v>
+      </c>
+      <c r="D34">
+        <v>0.0003097612643614411</v>
+      </c>
+      <c r="E34">
+        <v>0.004866513423621655</v>
+      </c>
+      <c r="F34">
+        <v>0.001116828760132194</v>
+      </c>
+      <c r="G34">
+        <v>0.001099024782888591</v>
+      </c>
+      <c r="H34">
+        <v>1.000284638240054</v>
+      </c>
+      <c r="I34">
+        <v>0.04944821139803387</v>
+      </c>
+      <c r="J34">
+        <v>0.06365157663822174</v>
+      </c>
+      <c r="K34">
+        <v>1.757815599441528</v>
+      </c>
+      <c r="L34">
+        <v>0.2785414755344391</v>
+      </c>
+      <c r="M34">
+        <v>3.643183946609497</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+      <c r="O34" t="s">
+        <v>203</v>
+      </c>
+      <c r="P34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001596394995526937</v>
+      </c>
+      <c r="D35">
+        <v>0.0009026023326441646</v>
+      </c>
+      <c r="E35">
+        <v>0.009660504758358002</v>
+      </c>
+      <c r="F35">
+        <v>0.001391380210407078</v>
+      </c>
+      <c r="G35">
+        <v>0.001314386958256364</v>
+      </c>
+      <c r="H35">
+        <v>1.000381383321754</v>
+      </c>
+      <c r="I35">
+        <v>0.04958593051550862</v>
+      </c>
+      <c r="J35">
+        <v>0.09343221038579941</v>
+      </c>
+      <c r="K35">
+        <v>18.21625518798828</v>
+      </c>
+      <c r="L35">
+        <v>0.5529320240020752</v>
+      </c>
+      <c r="M35">
+        <v>5.347718715667725</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+      <c r="O35" t="s">
+        <v>204</v>
+      </c>
+      <c r="P35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.003084327411105356</v>
+      </c>
+      <c r="D36">
+        <v>0.001810250803828239</v>
+      </c>
+      <c r="E36">
+        <v>0.01932119764387608</v>
+      </c>
+      <c r="F36">
+        <v>0.001633765641599894</v>
+      </c>
+      <c r="G36">
+        <v>0.001598564093001187</v>
+      </c>
+      <c r="H36">
+        <v>1.00055604023217</v>
+      </c>
+      <c r="I36">
+        <v>0.04966827973277471</v>
+      </c>
+      <c r="J36">
+        <v>0.09369247406721115</v>
+      </c>
+      <c r="K36">
+        <v>373.2153930664062</v>
+      </c>
+      <c r="L36">
+        <v>1.1058748960495</v>
+      </c>
+      <c r="M36">
+        <v>5.36261510848999</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" t="s">
+        <v>205</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.006002020575478256</v>
+      </c>
+      <c r="D37">
+        <v>0.003450605319812894</v>
+      </c>
+      <c r="E37">
+        <v>0.03862485662102699</v>
+      </c>
+      <c r="F37">
+        <v>0.001876332913525403</v>
+      </c>
+      <c r="G37">
+        <v>0.001895719673484564</v>
+      </c>
+      <c r="H37">
+        <v>1.000976176554914</v>
+      </c>
+      <c r="I37">
+        <v>0.04922790869503517</v>
+      </c>
+      <c r="J37">
+        <v>0.08933639526367188</v>
+      </c>
+      <c r="K37">
+        <v>79602.3984375</v>
+      </c>
+      <c r="L37">
+        <v>2.210745811462402</v>
+      </c>
+      <c r="M37">
+        <v>5.113289356231689</v>
+      </c>
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" t="s">
+        <v>206</v>
+      </c>
+      <c r="P37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01466441725149574</v>
+      </c>
+      <c r="D38">
+        <v>0.00813757162541151</v>
+      </c>
+      <c r="E38">
+        <v>0.09656237065792084</v>
+      </c>
+      <c r="F38">
+        <v>0.002097484888508916</v>
+      </c>
+      <c r="G38">
+        <v>0.002243058290332556</v>
+      </c>
+      <c r="H38">
+        <v>1.001510593235045</v>
+      </c>
+      <c r="I38">
+        <v>0.04967269914948109</v>
+      </c>
+      <c r="J38">
+        <v>0.08427269756793976</v>
+      </c>
+      <c r="K38">
+        <v>339534151680</v>
+      </c>
+      <c r="L38">
+        <v>5.526877880096436</v>
+      </c>
+      <c r="M38">
+        <v>4.823461532592773</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O38" t="s">
+        <v>207</v>
+      </c>
+      <c r="P38" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.02905036114274909</v>
+      </c>
+      <c r="D39">
+        <v>0.01578810624778271</v>
+      </c>
+      <c r="E39">
+        <v>0.1931803524494171</v>
+      </c>
+      <c r="F39">
+        <v>0.002204760443419218</v>
+      </c>
+      <c r="G39">
+        <v>0.002457100199535489</v>
+      </c>
+      <c r="H39">
+        <v>1.001916459388631</v>
+      </c>
+      <c r="I39">
+        <v>0.05004924434032918</v>
+      </c>
+      <c r="J39">
+        <v>0.0817272886633873</v>
+      </c>
+      <c r="K39">
+        <v>1.936391564862244E+22</v>
+      </c>
+      <c r="L39">
+        <v>11.05693817138672</v>
+      </c>
+      <c r="M39">
+        <v>4.67777156829834</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+      <c r="O39" t="s">
+        <v>208</v>
+      </c>
+      <c r="P39" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.07155484160835301</v>
+      </c>
+      <c r="D40">
+        <v>0.0383913442492485</v>
+      </c>
+      <c r="E40">
+        <v>0.4731627702713013</v>
+      </c>
+      <c r="F40">
+        <v>0.002302611013874412</v>
+      </c>
+      <c r="G40">
+        <v>0.002702792407944798</v>
+      </c>
+      <c r="H40">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I40">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J40">
+        <v>0.08113770931959152</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>27.08211135864258</v>
+      </c>
+      <c r="M40">
+        <v>4.644026279449463</v>
+      </c>
+      <c r="N40" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" t="s">
+        <v>209</v>
+      </c>
+      <c r="P40" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1501871143806354</v>
+      </c>
+      <c r="D41">
+        <v>0.07988638430833817</v>
+      </c>
+      <c r="E41">
+        <v>1.056071877479553</v>
+      </c>
+      <c r="F41">
+        <v>0.002430705353617668</v>
+      </c>
+      <c r="G41">
+        <v>0.002979565411806107</v>
+      </c>
+      <c r="H41">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I41">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J41">
+        <v>0.0756448358297348</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>60.44570159912109</v>
+      </c>
+      <c r="M41">
+        <v>4.329634189605713</v>
+      </c>
+      <c r="N41" t="s">
+        <v>150</v>
+      </c>
+      <c r="O41" t="s">
+        <v>210</v>
+      </c>
+      <c r="P41" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001452673186693237</v>
+      </c>
+      <c r="D42">
+        <v>-8.543957665096968E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001306027756072581</v>
+      </c>
+      <c r="F42">
+        <v>0.0009516610880382359</v>
+      </c>
+      <c r="G42">
+        <v>0.0009807803435251117</v>
+      </c>
+      <c r="H42">
+        <v>0.9998299389813911</v>
+      </c>
+      <c r="I42">
+        <v>0.04954694739876422</v>
+      </c>
+      <c r="J42">
+        <v>-0.06541942059993744</v>
+      </c>
+      <c r="K42">
+        <v>-0.2440850734710693</v>
+      </c>
+      <c r="L42">
+        <v>0.07475226372480392</v>
+      </c>
+      <c r="M42">
+        <v>-3.744369029998779</v>
+      </c>
+      <c r="N42" t="s">
+        <v>151</v>
+      </c>
+      <c r="O42" t="s">
+        <v>211</v>
+      </c>
+      <c r="P42" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.000184306447382204</v>
+      </c>
+      <c r="D43">
+        <v>6.335039506666362E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.0009223321685567498</v>
+      </c>
+      <c r="F43">
+        <v>0.001093453145585954</v>
+      </c>
+      <c r="G43">
+        <v>0.001073951716534793</v>
+      </c>
+      <c r="H43">
+        <v>0.9998917042842753</v>
+      </c>
+      <c r="I43">
+        <v>0.04965492453993256</v>
+      </c>
+      <c r="J43">
+        <v>0.06868501007556915</v>
+      </c>
+      <c r="K43">
+        <v>0.2304311990737915</v>
+      </c>
+      <c r="L43">
+        <v>0.05279092863202095</v>
+      </c>
+      <c r="M43">
+        <v>3.931279420852661</v>
+      </c>
+      <c r="N43" t="s">
+        <v>152</v>
+      </c>
+      <c r="O43" t="s">
+        <v>212</v>
+      </c>
+      <c r="P43" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.0002189096677534861</v>
+      </c>
+      <c r="D44">
+        <v>0.000138920295285061</v>
+      </c>
+      <c r="E44">
+        <v>0.001041725976392627</v>
+      </c>
+      <c r="F44">
+        <v>0.001193977659568191</v>
+      </c>
+      <c r="G44">
+        <v>0.001160440267995</v>
+      </c>
+      <c r="H44">
+        <v>0.9998789322575184</v>
+      </c>
+      <c r="I44">
+        <v>0.04977762445138232</v>
+      </c>
+      <c r="J44">
+        <v>0.1333558857440948</v>
+      </c>
+      <c r="K44">
+        <v>0.5760716199874878</v>
+      </c>
+      <c r="L44">
+        <v>0.05962459370493889</v>
+      </c>
+      <c r="M44">
+        <v>7.632804393768311</v>
+      </c>
+      <c r="N44" t="s">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s">
+        <v>213</v>
+      </c>
+      <c r="P44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0003587758707103237</v>
+      </c>
+      <c r="D45">
+        <v>0.00037326046731323</v>
+      </c>
+      <c r="E45">
+        <v>0.001434953766874969</v>
+      </c>
+      <c r="F45">
+        <v>0.001438421895727515</v>
+      </c>
+      <c r="G45">
+        <v>0.001365624950267375</v>
+      </c>
+      <c r="H45">
+        <v>1.000039003941615</v>
+      </c>
+      <c r="I45">
+        <v>0.04991247160628133</v>
+      </c>
+      <c r="J45">
+        <v>0.2601202130317688</v>
+      </c>
+      <c r="K45">
+        <v>2.395734786987305</v>
+      </c>
+      <c r="L45">
+        <v>0.0821315199136734</v>
+      </c>
+      <c r="M45">
+        <v>14.88833141326904</v>
+      </c>
+      <c r="N45" t="s">
+        <v>154</v>
+      </c>
+      <c r="O45" t="s">
+        <v>214</v>
+      </c>
+      <c r="P45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0005828366804811505</v>
+      </c>
+      <c r="D46">
+        <v>0.0005933745997026563</v>
+      </c>
+      <c r="E46">
+        <v>0.002435073489323258</v>
+      </c>
+      <c r="F46">
+        <v>0.001694732927717268</v>
+      </c>
+      <c r="G46">
+        <v>0.001662635593675077</v>
+      </c>
+      <c r="H46">
+        <v>1.000363774280563</v>
+      </c>
+      <c r="I46">
+        <v>0.04993123270079682</v>
+      </c>
+      <c r="J46">
+        <v>0.2436783164739609</v>
+      </c>
+      <c r="K46">
+        <v>5.983008861541748</v>
+      </c>
+      <c r="L46">
+        <v>0.1393747180700302</v>
+      </c>
+      <c r="M46">
+        <v>13.94725799560547</v>
+      </c>
+      <c r="N46" t="s">
+        <v>155</v>
+      </c>
+      <c r="O46" t="s">
+        <v>215</v>
+      </c>
+      <c r="P46" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.0009715172526751021</v>
+      </c>
+      <c r="D47">
+        <v>0.0008762780344113708</v>
+      </c>
+      <c r="E47">
+        <v>0.004479062743484974</v>
+      </c>
+      <c r="F47">
+        <v>0.00190169655252248</v>
+      </c>
+      <c r="G47">
+        <v>0.001960481284186244</v>
+      </c>
+      <c r="H47">
+        <v>1.000750176374612</v>
+      </c>
+      <c r="I47">
+        <v>0.04937533494287369</v>
+      </c>
+      <c r="J47">
+        <v>0.1956387013196945</v>
+      </c>
+      <c r="K47">
+        <v>16.62866401672363</v>
+      </c>
+      <c r="L47">
+        <v>0.2563652098178864</v>
+      </c>
+      <c r="M47">
+        <v>11.19764518737793</v>
+      </c>
+      <c r="N47" t="s">
+        <v>156</v>
+      </c>
+      <c r="O47" t="s">
+        <v>216</v>
+      </c>
+      <c r="P47" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.00203039234909373</v>
+      </c>
+      <c r="D48">
+        <v>0.001495273318141699</v>
+      </c>
+      <c r="E48">
+        <v>0.01078523881733418</v>
+      </c>
+      <c r="F48">
+        <v>0.002083746017888188</v>
+      </c>
+      <c r="G48">
+        <v>0.00230949860997498</v>
+      </c>
+      <c r="H48">
+        <v>1.001592277897386</v>
+      </c>
+      <c r="I48">
+        <v>0.04959042914746309</v>
+      </c>
+      <c r="J48">
+        <v>0.1386407166719437</v>
+      </c>
+      <c r="K48">
+        <v>132.5872344970703</v>
+      </c>
+      <c r="L48">
+        <v>0.617307722568512</v>
+      </c>
+      <c r="M48">
+        <v>7.935288906097412</v>
+      </c>
+      <c r="N48" t="s">
+        <v>157</v>
+      </c>
+      <c r="O48" t="s">
+        <v>217</v>
+      </c>
+      <c r="P48" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.003686721845921793</v>
+      </c>
+      <c r="D49">
+        <v>0.002442152705043554</v>
+      </c>
+      <c r="E49">
+        <v>0.02091952785849571</v>
+      </c>
+      <c r="F49">
+        <v>0.002205243101343513</v>
+      </c>
+      <c r="G49">
+        <v>0.002495332388207316</v>
+      </c>
+      <c r="H49">
+        <v>1.001903183156168</v>
+      </c>
+      <c r="I49">
+        <v>0.05022121517931358</v>
+      </c>
+      <c r="J49">
+        <v>0.1167403385043144</v>
+      </c>
+      <c r="K49">
+        <v>2952.177490234375</v>
+      </c>
+      <c r="L49">
+        <v>1.197357416152954</v>
+      </c>
+      <c r="M49">
+        <v>6.681790828704834</v>
+      </c>
+      <c r="N49" t="s">
+        <v>158</v>
+      </c>
+      <c r="O49" t="s">
+        <v>218</v>
+      </c>
+      <c r="P49" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.008900830612854854</v>
+      </c>
+      <c r="D50">
+        <v>0.005312644876539707</v>
+      </c>
+      <c r="E50">
+        <v>0.05486489459872246</v>
+      </c>
+      <c r="F50">
+        <v>0.002290616044774652</v>
+      </c>
+      <c r="G50">
+        <v>0.002716473769396544</v>
+      </c>
+      <c r="H50">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I50">
+        <v>0.05582449286615769</v>
+      </c>
+      <c r="J50">
+        <v>0.09683140367269516</v>
+      </c>
+      <c r="K50">
+        <v>34562328</v>
+      </c>
+      <c r="L50">
+        <v>3.140266418457031</v>
+      </c>
+      <c r="M50">
+        <v>5.542276382446289</v>
+      </c>
+      <c r="N50" t="s">
+        <v>159</v>
+      </c>
+      <c r="O50" t="s">
+        <v>219</v>
+      </c>
+      <c r="P50" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01679805344202947</v>
+      </c>
+      <c r="D51">
+        <v>0.009583594277501106</v>
+      </c>
+      <c r="E51">
+        <v>0.1009650751948357</v>
+      </c>
+      <c r="F51">
+        <v>0.002393747447058558</v>
+      </c>
+      <c r="G51">
+        <v>0.002908714581280947</v>
+      </c>
+      <c r="H51">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I51">
+        <v>0.06535901646999488</v>
+      </c>
+      <c r="J51">
+        <v>0.09491989761590958</v>
+      </c>
+      <c r="K51">
+        <v>37163957747712</v>
+      </c>
+      <c r="L51">
+        <v>5.778872489929199</v>
+      </c>
+      <c r="M51">
+        <v>5.432868480682373</v>
+      </c>
+      <c r="N51" t="s">
+        <v>160</v>
+      </c>
+      <c r="O51" t="s">
+        <v>220</v>
+      </c>
+      <c r="P51" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001609711555171446</v>
+      </c>
+      <c r="D52">
+        <v>0.0002514284860808402</v>
+      </c>
+      <c r="E52">
+        <v>0.0006804469740018249</v>
+      </c>
+      <c r="F52">
+        <v>0.001054380903951824</v>
+      </c>
+      <c r="G52">
+        <v>0.001064090407453477</v>
+      </c>
+      <c r="H52">
+        <v>0.9992264509690679</v>
+      </c>
+      <c r="I52">
+        <v>0.05003635878674079</v>
+      </c>
+      <c r="J52">
+        <v>0.3695048987865448</v>
+      </c>
+      <c r="K52">
+        <v>1.27851390838623</v>
+      </c>
+      <c r="L52">
+        <v>0.03894630074501038</v>
+      </c>
+      <c r="M52">
+        <v>21.14911270141602</v>
+      </c>
+      <c r="N52" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" t="s">
+        <v>221</v>
+      </c>
+      <c r="P52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0001917441394866527</v>
+      </c>
+      <c r="D53">
+        <v>0.0003003851743414998</v>
+      </c>
+      <c r="E53">
+        <v>0.0007495165918953717</v>
+      </c>
+      <c r="F53">
+        <v>0.00112006370909512</v>
+      </c>
+      <c r="G53">
+        <v>0.001118688029237092</v>
+      </c>
+      <c r="H53">
+        <v>0.9991662533232877</v>
+      </c>
+      <c r="I53">
+        <v>0.05027654503343248</v>
+      </c>
+      <c r="J53">
+        <v>0.4007718861103058</v>
+      </c>
+      <c r="K53">
+        <v>1.675100326538086</v>
+      </c>
+      <c r="L53">
+        <v>0.04289959371089935</v>
+      </c>
+      <c r="M53">
+        <v>22.938720703125</v>
+      </c>
+      <c r="N53" t="s">
+        <v>162</v>
+      </c>
+      <c r="O53" t="s">
+        <v>222</v>
+      </c>
+      <c r="P53" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0002157409029304292</v>
+      </c>
+      <c r="D54">
+        <v>0.0003364321601111442</v>
+      </c>
+      <c r="E54">
+        <v>0.0007965426193550229</v>
+      </c>
+      <c r="F54">
+        <v>0.001184976077638566</v>
+      </c>
+      <c r="G54">
+        <v>0.001159124658443034</v>
+      </c>
+      <c r="H54">
+        <v>0.9991432150169227</v>
+      </c>
+      <c r="I54">
+        <v>0.05049053150504521</v>
+      </c>
+      <c r="J54">
+        <v>0.4223655462265015</v>
+      </c>
+      <c r="K54">
+        <v>2.009847164154053</v>
+      </c>
+      <c r="L54">
+        <v>0.04559119418263435</v>
+      </c>
+      <c r="M54">
+        <v>24.17466354370117</v>
+      </c>
+      <c r="N54" t="s">
+        <v>163</v>
+      </c>
+      <c r="O54" t="s">
+        <v>223</v>
+      </c>
+      <c r="P54" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.0002938508267660958</v>
+      </c>
+      <c r="D55">
+        <v>0.0004502674273680896</v>
+      </c>
+      <c r="E55">
+        <v>0.0009489997173659503</v>
+      </c>
+      <c r="F55">
+        <v>0.0013847112422809</v>
+      </c>
+      <c r="G55">
+        <v>0.001387387048453093</v>
+      </c>
+      <c r="H55">
+        <v>0.9993283495712529</v>
+      </c>
+      <c r="I55">
+        <v>0.05067371860725085</v>
+      </c>
+      <c r="J55">
+        <v>0.4744652807712555</v>
+      </c>
+      <c r="K55">
+        <v>3.369718074798584</v>
+      </c>
+      <c r="L55">
+        <v>0.05431728065013885</v>
+      </c>
+      <c r="M55">
+        <v>27.15666198730469</v>
+      </c>
+      <c r="N55" t="s">
+        <v>164</v>
+      </c>
+      <c r="O55" t="s">
+        <v>224</v>
+      </c>
+      <c r="P55" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0003763599395270181</v>
+      </c>
+      <c r="D56">
+        <v>0.0005541474092751741</v>
+      </c>
+      <c r="E56">
+        <v>0.001109405653551221</v>
+      </c>
+      <c r="F56">
+        <v>0.001628901343792677</v>
+      </c>
+      <c r="G56">
+        <v>0.0017298354068771</v>
+      </c>
+      <c r="H56">
+        <v>0.9997528700456052</v>
+      </c>
+      <c r="I56">
+        <v>0.0505113604909533</v>
+      </c>
+      <c r="J56">
+        <v>0.4994993507862091</v>
+      </c>
+      <c r="K56">
+        <v>5.141501903533936</v>
+      </c>
+      <c r="L56">
+        <v>0.06349833309650421</v>
+      </c>
+      <c r="M56">
+        <v>28.58951950073242</v>
+      </c>
+      <c r="N56" t="s">
+        <v>165</v>
+      </c>
+      <c r="O56" t="s">
+        <v>225</v>
+      </c>
+      <c r="P56" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0004556898723139521</v>
+      </c>
+      <c r="D57">
+        <v>0.0006346158916130662</v>
+      </c>
+      <c r="E57">
+        <v>0.001333103748038411</v>
+      </c>
+      <c r="F57">
+        <v>0.001761837513186038</v>
+      </c>
+      <c r="G57">
+        <v>0.001964873168617487</v>
+      </c>
+      <c r="H57">
+        <v>1.000575122726706</v>
+      </c>
+      <c r="I57">
+        <v>0.04937120610060882</v>
+      </c>
+      <c r="J57">
+        <v>0.4760438799858093</v>
+      </c>
+      <c r="K57">
+        <v>6.992632865905762</v>
+      </c>
+      <c r="L57">
+        <v>0.07630199193954468</v>
+      </c>
+      <c r="M57">
+        <v>27.24701499938965</v>
+      </c>
+      <c r="N57" t="s">
+        <v>166</v>
+      </c>
+      <c r="O57" t="s">
+        <v>226</v>
+      </c>
+      <c r="P57" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0005493273124272009</v>
+      </c>
+      <c r="D58">
+        <v>0.0007530554430559278</v>
+      </c>
+      <c r="E58">
+        <v>0.001837686519138515</v>
+      </c>
+      <c r="F58">
+        <v>0.001932587241753936</v>
+      </c>
+      <c r="G58">
+        <v>0.002300990046933293</v>
+      </c>
+      <c r="H58">
+        <v>1.001095333315624</v>
+      </c>
+      <c r="I58">
+        <v>0.04999764191846216</v>
+      </c>
+      <c r="J58">
+        <v>0.4097844958305359</v>
+      </c>
+      <c r="K58">
+        <v>10.77580833435059</v>
+      </c>
+      <c r="L58">
+        <v>0.1051824688911438</v>
+      </c>
+      <c r="M58">
+        <v>23.45456886291504</v>
+      </c>
+      <c r="N58" t="s">
+        <v>167</v>
+      </c>
+      <c r="O58" t="s">
+        <v>227</v>
+      </c>
+      <c r="P58" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0006123581218294095</v>
+      </c>
+      <c r="D59">
+        <v>0.0008488058228977025</v>
+      </c>
+      <c r="E59">
+        <v>0.002385282656177878</v>
+      </c>
+      <c r="F59">
+        <v>0.00197509559802711</v>
+      </c>
+      <c r="G59">
+        <v>0.002519394038245082</v>
+      </c>
+      <c r="H59">
+        <v>1.001180293880885</v>
+      </c>
+      <c r="I59">
+        <v>0.05076132394791717</v>
+      </c>
+      <c r="J59">
+        <v>0.3558512628078461</v>
+      </c>
+      <c r="K59">
+        <v>15.10921669006348</v>
+      </c>
+      <c r="L59">
+        <v>0.1365248709917068</v>
+      </c>
+      <c r="M59">
+        <v>20.36762809753418</v>
+      </c>
+      <c r="N59" t="s">
+        <v>168</v>
+      </c>
+      <c r="O59" t="s">
+        <v>228</v>
+      </c>
+      <c r="P59" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0006881899190547753</v>
+      </c>
+      <c r="D60">
+        <v>0.0010096684563905</v>
+      </c>
+      <c r="E60">
+        <v>0.003746364498510957</v>
+      </c>
+      <c r="F60">
+        <v>0.00200557941570878</v>
+      </c>
+      <c r="G60">
+        <v>0.002711254172027111</v>
+      </c>
+      <c r="H60">
+        <v>1.002196227884722</v>
+      </c>
+      <c r="I60">
+        <v>0.05627726249427821</v>
+      </c>
+      <c r="J60">
+        <v>0.2695061862468719</v>
+      </c>
+      <c r="K60">
+        <v>26.27899932861328</v>
+      </c>
+      <c r="L60">
+        <v>0.2144282311201096</v>
+      </c>
+      <c r="M60">
+        <v>15.42555046081543</v>
+      </c>
+      <c r="N60" t="s">
+        <v>169</v>
+      </c>
+      <c r="O60" t="s">
+        <v>229</v>
+      </c>
+      <c r="P60" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.0007390135082216226</v>
+      </c>
+      <c r="D61">
+        <v>0.001088770688511431</v>
+      </c>
+      <c r="E61">
+        <v>0.005083249881863594</v>
+      </c>
+      <c r="F61">
+        <v>0.002038101898506284</v>
+      </c>
+      <c r="G61">
+        <v>0.002894158707931638</v>
+      </c>
+      <c r="H61">
+        <v>1.003335373317013</v>
+      </c>
+      <c r="I61">
+        <v>0.06582658500346944</v>
+      </c>
+      <c r="J61">
+        <v>0.2141879200935364</v>
+      </c>
+      <c r="K61">
+        <v>34.33121871948242</v>
+      </c>
+      <c r="L61">
+        <v>0.2909466624259949</v>
+      </c>
+      <c r="M61">
+        <v>12.25933456420898</v>
+      </c>
+      <c r="N61" t="s">
+        <v>170</v>
+      </c>
+      <c r="O61" t="s">
+        <v>230</v>
+      </c>
+      <c r="P61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2">
+        <v>0.0008682085710513829</v>
+      </c>
+      <c r="D2">
+        <v>-0.004355625715106726</v>
+      </c>
+      <c r="E2">
+        <v>0.08704543858766556</v>
+      </c>
+      <c r="F2">
+        <v>0.0008046997245401144</v>
+      </c>
+      <c r="G2">
+        <v>0.0009176492458209395</v>
+      </c>
+      <c r="H2">
+        <v>1.000394839999947</v>
+      </c>
+      <c r="I2">
+        <v>0.0491364628575314</v>
+      </c>
+      <c r="J2">
+        <v>-0.05003852769732475</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999994039535522</v>
+      </c>
+      <c r="L2">
+        <v>4.982163429260254</v>
+      </c>
+      <c r="M2">
+        <v>-2.864022731781006</v>
+      </c>
+      <c r="N2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O2" t="s">
+        <v>351</v>
+      </c>
+      <c r="P2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>0.001155806693910404</v>
+      </c>
+      <c r="D3">
+        <v>-0.005874110851436853</v>
+      </c>
+      <c r="E3">
+        <v>0.1179485023021698</v>
+      </c>
+      <c r="F3">
+        <v>0.0009121673065237701</v>
+      </c>
+      <c r="G3">
+        <v>0.0009611376444809139</v>
+      </c>
+      <c r="H3">
+        <v>1.000607425250309</v>
+      </c>
+      <c r="I3">
+        <v>0.04906167845176727</v>
+      </c>
+      <c r="J3">
+        <v>-0.04980233684182167</v>
+      </c>
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3">
+        <v>6.750941753387451</v>
+      </c>
+      <c r="M3">
+        <v>-2.850503921508789</v>
+      </c>
+      <c r="N3" t="s">
+        <v>292</v>
+      </c>
+      <c r="O3" t="s">
+        <v>352</v>
+      </c>
+      <c r="P3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.001441823582502342</v>
+      </c>
+      <c r="D4">
+        <v>-0.002733554458245635</v>
+      </c>
+      <c r="E4">
+        <v>0.08060475438833237</v>
+      </c>
+      <c r="F4">
+        <v>0.001000638934783638</v>
+      </c>
+      <c r="G4">
+        <v>0.001031924737617373</v>
+      </c>
+      <c r="H4">
+        <v>1.000705438417328</v>
+      </c>
+      <c r="I4">
+        <v>0.04910310339370038</v>
+      </c>
+      <c r="J4">
+        <v>-0.03391306847333908</v>
+      </c>
+      <c r="K4">
+        <v>-0.9998725056648254</v>
+      </c>
+      <c r="L4">
+        <v>4.613522052764893</v>
+      </c>
+      <c r="M4">
+        <v>-1.941060304641724</v>
+      </c>
+      <c r="N4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O4" t="s">
+        <v>353</v>
+      </c>
+      <c r="P4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>0.002851287454675742</v>
+      </c>
+      <c r="D5">
+        <v>-0.001982660498470068</v>
+      </c>
+      <c r="E5">
+        <v>0.09021203219890594</v>
+      </c>
+      <c r="F5">
+        <v>0.001273776753805578</v>
+      </c>
+      <c r="G5">
+        <v>0.001251215115189552</v>
+      </c>
+      <c r="H5">
+        <v>1.000804519903749</v>
+      </c>
+      <c r="I5">
+        <v>0.04918094523923637</v>
+      </c>
+      <c r="J5">
+        <v>-0.02197778411209583</v>
+      </c>
+      <c r="K5">
+        <v>-0.9984991550445557</v>
+      </c>
+      <c r="L5">
+        <v>5.163407325744629</v>
+      </c>
+      <c r="M5">
+        <v>-1.257928133010864</v>
+      </c>
+      <c r="N5" t="s">
+        <v>294</v>
+      </c>
+      <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6">
+        <v>0.005627393239646426</v>
+      </c>
+      <c r="D6">
+        <v>0.002843153197318316</v>
+      </c>
+      <c r="E6">
+        <v>0.01936274580657482</v>
+      </c>
+      <c r="F6">
+        <v>0.001538118696771562</v>
+      </c>
+      <c r="G6">
+        <v>0.001451674848794937</v>
+      </c>
+      <c r="H6">
+        <v>1.000908527367737</v>
+      </c>
+      <c r="I6">
+        <v>0.04930344385720799</v>
+      </c>
+      <c r="J6">
+        <v>0.1468362659215927</v>
+      </c>
+      <c r="K6">
+        <v>10947.0439453125</v>
+      </c>
+      <c r="L6">
+        <v>1.108252882957458</v>
+      </c>
+      <c r="M6">
+        <v>8.404372215270996</v>
+      </c>
+      <c r="N6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O6" t="s">
+        <v>355</v>
+      </c>
+      <c r="P6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>0.01114214872824768</v>
+      </c>
+      <c r="D7">
+        <v>0.005977197084575891</v>
+      </c>
+      <c r="E7">
+        <v>0.03922593966126442</v>
+      </c>
+      <c r="F7">
+        <v>0.001771919429302216</v>
+      </c>
+      <c r="G7">
+        <v>0.001749330433085561</v>
+      </c>
+      <c r="H7">
+        <v>1.001181319183715</v>
+      </c>
+      <c r="I7">
+        <v>0.04903757134828177</v>
+      </c>
+      <c r="J7">
+        <v>0.1523786783218384</v>
+      </c>
+      <c r="K7">
+        <v>301074464</v>
+      </c>
+      <c r="L7">
+        <v>2.245149612426758</v>
+      </c>
+      <c r="M7">
+        <v>8.721599578857422</v>
+      </c>
+      <c r="N7" t="s">
+        <v>296</v>
+      </c>
+      <c r="O7" t="s">
+        <v>356</v>
+      </c>
+      <c r="P7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8">
+        <v>0.02755149262163994</v>
+      </c>
+      <c r="D8">
+        <v>0.01546976994723082</v>
+      </c>
+      <c r="E8">
+        <v>0.1150166317820549</v>
+      </c>
+      <c r="F8">
+        <v>0.002067901194095612</v>
+      </c>
+      <c r="G8">
+        <v>0.00213916483335197</v>
+      </c>
+      <c r="H8">
+        <v>1.0015405077113</v>
+      </c>
+      <c r="I8">
+        <v>0.04965469487407401</v>
+      </c>
+      <c r="J8">
+        <v>0.1345002800226212</v>
+      </c>
+      <c r="K8">
+        <v>6.936122701652634E+21</v>
+      </c>
+      <c r="L8">
+        <v>6.583132266998291</v>
+      </c>
+      <c r="M8">
+        <v>7.698305130004883</v>
+      </c>
+      <c r="N8" t="s">
+        <v>297</v>
+      </c>
+      <c r="O8" t="s">
+        <v>357</v>
+      </c>
+      <c r="P8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>0.05489586353640788</v>
+      </c>
+      <c r="D9">
+        <v>0.03145071119070053</v>
+      </c>
+      <c r="E9">
+        <v>0.2492879033088684</v>
+      </c>
+      <c r="F9">
+        <v>0.00223531830124557</v>
+      </c>
+      <c r="G9">
+        <v>0.002405272331088781</v>
+      </c>
+      <c r="H9">
+        <v>1.001843243623203</v>
+      </c>
+      <c r="I9">
+        <v>0.05018541637522048</v>
+      </c>
+      <c r="J9">
+        <v>0.126162201166153</v>
+      </c>
+      <c r="K9" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9">
+        <v>14.26832962036133</v>
+      </c>
+      <c r="M9">
+        <v>7.22106409072876</v>
+      </c>
+      <c r="N9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O9" t="s">
+        <v>358</v>
+      </c>
+      <c r="P9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10">
+        <v>0.1380643129590552</v>
+      </c>
+      <c r="D10">
+        <v>0.07900523394346237</v>
+      </c>
+      <c r="E10">
+        <v>0.6421134471893311</v>
+      </c>
+      <c r="F10">
+        <v>0.002376535208895802</v>
+      </c>
+      <c r="G10">
+        <v>0.002678487915545702</v>
+      </c>
+      <c r="H10">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I10">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J10">
+        <v>0.1230393722653389</v>
+      </c>
+      <c r="K10" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10">
+        <v>36.75223159790039</v>
+      </c>
+      <c r="M10">
+        <v>7.042324542999268</v>
+      </c>
+      <c r="N10" t="s">
+        <v>299</v>
+      </c>
+      <c r="O10" t="s">
+        <v>359</v>
+      </c>
+      <c r="P10" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>0.2693886325273367</v>
+      </c>
+      <c r="D11">
+        <v>0.1528946608304977</v>
+      </c>
+      <c r="E11">
+        <v>1.166545629501343</v>
+      </c>
+      <c r="F11">
+        <v>0.002486004494130611</v>
+      </c>
+      <c r="G11">
+        <v>0.002944711828604341</v>
+      </c>
+      <c r="H11">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I11">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J11">
+        <v>0.131066158413887</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11">
+        <v>66.76881408691406</v>
+      </c>
+      <c r="M11">
+        <v>7.501748561859131</v>
+      </c>
+      <c r="N11" t="s">
+        <v>300</v>
+      </c>
+      <c r="O11" t="s">
+        <v>360</v>
+      </c>
+      <c r="P11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>0.001362675296290508</v>
+      </c>
+      <c r="D12">
+        <v>-0.0001566971623105928</v>
+      </c>
+      <c r="E12">
+        <v>0.008735238574445248</v>
+      </c>
+      <c r="F12">
+        <v>0.0008107501780614257</v>
+      </c>
+      <c r="G12">
+        <v>0.0009207917610183358</v>
+      </c>
+      <c r="H12">
+        <v>1.000345855092125</v>
+      </c>
+      <c r="I12">
+        <v>0.04919556952786697</v>
+      </c>
+      <c r="J12">
+        <v>-0.01793850958347321</v>
+      </c>
+      <c r="K12">
+        <v>-0.4015375375747681</v>
+      </c>
+      <c r="L12">
+        <v>0.4999731779098511</v>
+      </c>
+      <c r="M12">
+        <v>-1.026734828948975</v>
+      </c>
+      <c r="N12" t="s">
+        <v>301</v>
+      </c>
+      <c r="O12" t="s">
+        <v>361</v>
+      </c>
+      <c r="P12" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>0.001814628681600702</v>
+      </c>
+      <c r="D13">
+        <v>0.0003182529180776328</v>
+      </c>
+      <c r="E13">
+        <v>0.01075427141040564</v>
+      </c>
+      <c r="F13">
+        <v>0.000919578829780221</v>
+      </c>
+      <c r="G13">
+        <v>0.0009639117633923888</v>
+      </c>
+      <c r="H13">
+        <v>1.000513973081593</v>
+      </c>
+      <c r="I13">
+        <v>0.04913460828178437</v>
+      </c>
+      <c r="J13">
+        <v>0.02959316410124302</v>
+      </c>
+      <c r="K13">
+        <v>1.836435556411743</v>
+      </c>
+      <c r="L13">
+        <v>0.6155352592468262</v>
+      </c>
+      <c r="M13">
+        <v>1.693804740905762</v>
+      </c>
+      <c r="N13" t="s">
+        <v>302</v>
+      </c>
+      <c r="O13" t="s">
+        <v>362</v>
+      </c>
+      <c r="P13" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>0.00226415386954324</v>
+      </c>
+      <c r="D14">
+        <v>0.000877188635058701</v>
+      </c>
+      <c r="E14">
+        <v>0.01208039373159409</v>
+      </c>
+      <c r="F14">
+        <v>0.001020393916405737</v>
+      </c>
+      <c r="G14">
+        <v>0.001038802322000265</v>
+      </c>
+      <c r="H14">
+        <v>1.00058566999439</v>
+      </c>
+      <c r="I14">
+        <v>0.04917503289073173</v>
+      </c>
+      <c r="J14">
+        <v>0.07261258363723755</v>
+      </c>
+      <c r="K14">
+        <v>16.6768798828125</v>
+      </c>
+      <c r="L14">
+        <v>0.6914376616477966</v>
+      </c>
+      <c r="M14">
+        <v>4.156079292297363</v>
+      </c>
+      <c r="N14" t="s">
+        <v>303</v>
+      </c>
+      <c r="O14" t="s">
+        <v>363</v>
+      </c>
+      <c r="P14" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>0.004492140234352036</v>
+      </c>
+      <c r="D15">
+        <v>0.002851103898137808</v>
+      </c>
+      <c r="E15">
+        <v>0.03188040480017662</v>
+      </c>
+      <c r="F15">
+        <v>0.001295118825510144</v>
+      </c>
+      <c r="G15">
+        <v>0.001247474108822644</v>
+      </c>
+      <c r="H15">
+        <v>1.00068401159735</v>
+      </c>
+      <c r="I15">
+        <v>0.04929657659346138</v>
+      </c>
+      <c r="J15">
+        <v>0.08943123370409012</v>
+      </c>
+      <c r="K15">
+        <v>11236.4501953125</v>
+      </c>
+      <c r="L15">
+        <v>1.824717998504639</v>
+      </c>
+      <c r="M15">
+        <v>5.118717670440674</v>
+      </c>
+      <c r="N15" t="s">
+        <v>304</v>
+      </c>
+      <c r="O15" t="s">
+        <v>364</v>
+      </c>
+      <c r="P15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>0.008899980816605915</v>
+      </c>
+      <c r="D16">
+        <v>0.005216542631387711</v>
+      </c>
+      <c r="E16">
+        <v>0.04357660934329033</v>
+      </c>
+      <c r="F16">
+        <v>0.001570284832268953</v>
+      </c>
+      <c r="G16">
+        <v>0.001490175724029541</v>
+      </c>
+      <c r="H16">
+        <v>1.000841019025251</v>
+      </c>
+      <c r="I16">
+        <v>0.0493521883977284</v>
+      </c>
+      <c r="J16">
+        <v>0.1197096928954124</v>
+      </c>
+      <c r="K16">
+        <v>25270704</v>
+      </c>
+      <c r="L16">
+        <v>2.494166135787964</v>
+      </c>
+      <c r="M16">
+        <v>6.851746082305908</v>
+      </c>
+      <c r="N16" t="s">
+        <v>305</v>
+      </c>
+      <c r="O16" t="s">
+        <v>365</v>
+      </c>
+      <c r="P16" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17">
+        <v>0.01765532134556722</v>
+      </c>
+      <c r="D17">
+        <v>0.009920091368257999</v>
+      </c>
+      <c r="E17">
+        <v>0.07437240332365036</v>
+      </c>
+      <c r="F17">
+        <v>0.001802277169190347</v>
+      </c>
+      <c r="G17">
+        <v>0.001789689296856523</v>
+      </c>
+      <c r="H17">
+        <v>1.001138072751286</v>
+      </c>
+      <c r="I17">
+        <v>0.04907729531054493</v>
+      </c>
+      <c r="J17">
+        <v>0.13338403403759</v>
+      </c>
+      <c r="K17">
+        <v>110736923688960</v>
+      </c>
+      <c r="L17">
+        <v>4.256804943084717</v>
+      </c>
+      <c r="M17">
+        <v>7.634415626525879</v>
+      </c>
+      <c r="N17" t="s">
+        <v>306</v>
+      </c>
+      <c r="O17" t="s">
+        <v>366</v>
+      </c>
+      <c r="P17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>0.04383327158534721</v>
+      </c>
+      <c r="D18">
+        <v>0.02431897446513176</v>
+      </c>
+      <c r="E18">
+        <v>0.1866454035043716</v>
+      </c>
+      <c r="F18">
+        <v>0.002072424162179232</v>
+      </c>
+      <c r="G18">
+        <v>0.002178006106987596</v>
+      </c>
+      <c r="H18">
+        <v>1.001512422714679</v>
+      </c>
+      <c r="I18">
+        <v>0.04963617045684296</v>
+      </c>
+      <c r="J18">
+        <v>0.130295068025589</v>
+      </c>
+      <c r="K18">
+        <v>1.533614218646446E+34</v>
+      </c>
+      <c r="L18">
+        <v>10.68290138244629</v>
+      </c>
+      <c r="M18">
+        <v>7.457614421844482</v>
+      </c>
+      <c r="N18" t="s">
+        <v>307</v>
+      </c>
+      <c r="O18" t="s">
+        <v>367</v>
+      </c>
+      <c r="P18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>0.0866939234347017</v>
+      </c>
+      <c r="D19">
+        <v>0.04774051532149315</v>
+      </c>
+      <c r="E19">
+        <v>0.3675444722175598</v>
+      </c>
+      <c r="F19">
+        <v>0.002216756576672196</v>
+      </c>
+      <c r="G19">
+        <v>0.002428477397188544</v>
+      </c>
+      <c r="H19">
+        <v>1.00192085169799</v>
+      </c>
+      <c r="I19">
+        <v>0.05009964352345458</v>
+      </c>
+      <c r="J19">
+        <v>0.1298904418945312</v>
+      </c>
+      <c r="K19" t="s">
+        <v>110</v>
+      </c>
+      <c r="L19">
+        <v>21.03690528869629</v>
+      </c>
+      <c r="M19">
+        <v>7.434454917907715</v>
+      </c>
+      <c r="N19" t="s">
+        <v>308</v>
+      </c>
+      <c r="O19" t="s">
+        <v>368</v>
+      </c>
+      <c r="P19" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20">
+        <v>0.2177230139752587</v>
+      </c>
+      <c r="D20">
+        <v>0.1204745396971703</v>
+      </c>
+      <c r="E20">
+        <v>0.9480220079421997</v>
+      </c>
+      <c r="F20">
+        <v>0.002396577736362815</v>
+      </c>
+      <c r="G20">
+        <v>0.00271627283655107</v>
+      </c>
+      <c r="H20">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I20">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J20">
+        <v>0.1270799040794373</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>54.26132202148438</v>
+      </c>
+      <c r="M20">
+        <v>7.273590087890625</v>
+      </c>
+      <c r="N20" t="s">
+        <v>309</v>
+      </c>
+      <c r="O20" t="s">
+        <v>369</v>
+      </c>
+      <c r="P20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21">
+        <v>0.4282119954750537</v>
+      </c>
+      <c r="D21">
+        <v>0.2494845539331436</v>
+      </c>
+      <c r="E21">
+        <v>2.076434373855591</v>
+      </c>
+      <c r="F21">
+        <v>0.002490456914529204</v>
+      </c>
+      <c r="G21">
+        <v>0.002964297076687217</v>
+      </c>
+      <c r="H21">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I21">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J21">
+        <v>0.1201504617929459</v>
+      </c>
+      <c r="K21" t="s">
+        <v>110</v>
+      </c>
+      <c r="L21">
+        <v>118.847526550293</v>
+      </c>
+      <c r="M21">
+        <v>6.876974105834961</v>
+      </c>
+      <c r="N21" t="s">
+        <v>310</v>
+      </c>
+      <c r="O21" t="s">
+        <v>370</v>
+      </c>
+      <c r="P21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>0.0005389351313093522</v>
+      </c>
+      <c r="D22">
+        <v>-0.0002962191065307707</v>
+      </c>
+      <c r="E22">
+        <v>0.002936178585514426</v>
+      </c>
+      <c r="F22">
+        <v>0.0008259646128863096</v>
+      </c>
+      <c r="G22">
+        <v>0.0009209691779688001</v>
+      </c>
+      <c r="H22">
+        <v>1.00026127993147</v>
+      </c>
+      <c r="I22">
+        <v>0.0492697785236048</v>
+      </c>
+      <c r="J22">
+        <v>-0.1008859276771545</v>
+      </c>
+      <c r="K22">
+        <v>-0.6211481094360352</v>
+      </c>
+      <c r="L22">
+        <v>0.1680561453104019</v>
+      </c>
+      <c r="M22">
+        <v>-5.77434253692627</v>
+      </c>
+      <c r="N22" t="s">
+        <v>311</v>
+      </c>
+      <c r="O22" t="s">
+        <v>371</v>
+      </c>
+      <c r="P22" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>0.0007152373517759848</v>
+      </c>
+      <c r="D23">
+        <v>-8.961707499111071E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.003608693135902286</v>
+      </c>
+      <c r="F23">
+        <v>0.0009471705416217446</v>
+      </c>
+      <c r="G23">
+        <v>0.0009754634229466319</v>
+      </c>
+      <c r="H23">
+        <v>1.000423174828929</v>
+      </c>
+      <c r="I23">
+        <v>0.0492137282965066</v>
+      </c>
+      <c r="J23">
+        <v>-0.02483366429805756</v>
+      </c>
+      <c r="K23">
+        <v>-0.2544935345649719</v>
+      </c>
+      <c r="L23">
+        <v>0.2065484225749969</v>
+      </c>
+      <c r="M23">
+        <v>-1.421388268470764</v>
+      </c>
+      <c r="N23" t="s">
+        <v>312</v>
+      </c>
+      <c r="O23" t="s">
+        <v>372</v>
+      </c>
+      <c r="P23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24">
+        <v>0.0008888753618020398</v>
+      </c>
+      <c r="D24">
+        <v>0.0001236918178619817</v>
+      </c>
+      <c r="E24">
+        <v>0.004459577612578869</v>
+      </c>
+      <c r="F24">
+        <v>0.001059117610566318</v>
+      </c>
+      <c r="G24">
+        <v>0.001058269990608096</v>
+      </c>
+      <c r="H24">
+        <v>1.000471172761078</v>
+      </c>
+      <c r="I24">
+        <v>0.04929255142664427</v>
+      </c>
+      <c r="J24">
+        <v>0.02773621864616871</v>
+      </c>
+      <c r="K24">
+        <v>0.4998193979263306</v>
+      </c>
+      <c r="L24">
+        <v>0.255249947309494</v>
+      </c>
+      <c r="M24">
+        <v>1.587520003318787</v>
+      </c>
+      <c r="N24" t="s">
+        <v>313</v>
+      </c>
+      <c r="O24" t="s">
+        <v>373</v>
+      </c>
+      <c r="P24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25">
+        <v>0.001732315621047638</v>
+      </c>
+      <c r="D25">
+        <v>0.0008629045332781971</v>
+      </c>
+      <c r="E25">
+        <v>0.008674106560647488</v>
+      </c>
+      <c r="F25">
+        <v>0.00133297243155539</v>
+      </c>
+      <c r="G25">
+        <v>0.001275826012715697</v>
+      </c>
+      <c r="H25">
+        <v>1.000573031737882</v>
+      </c>
+      <c r="I25">
+        <v>0.04942998091537426</v>
+      </c>
+      <c r="J25">
+        <v>0.09948050975799561</v>
+      </c>
+      <c r="K25">
+        <v>15.87485885620117</v>
+      </c>
+      <c r="L25">
+        <v>0.4964742064476013</v>
+      </c>
+      <c r="M25">
+        <v>5.693901538848877</v>
+      </c>
+      <c r="N25" t="s">
+        <v>314</v>
+      </c>
+      <c r="O25" t="s">
+        <v>374</v>
+      </c>
+      <c r="P25" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0.003370777527036016</v>
+      </c>
+      <c r="D26">
+        <v>0.00190205592662096</v>
+      </c>
+      <c r="E26">
+        <v>0.01685513369739056</v>
+      </c>
+      <c r="F26">
+        <v>0.001602189848199487</v>
+      </c>
+      <c r="G26">
+        <v>0.001539202174171805</v>
+      </c>
+      <c r="H26">
+        <v>1.000731694822443</v>
+      </c>
+      <c r="I26">
+        <v>0.04948189474792315</v>
+      </c>
+      <c r="J26">
+        <v>0.112847276031971</v>
+      </c>
+      <c r="K26">
+        <v>504.4110412597656</v>
+      </c>
+      <c r="L26">
+        <v>0.9647263288497925</v>
+      </c>
+      <c r="M26">
+        <v>6.458966255187988</v>
+      </c>
+      <c r="N26" t="s">
+        <v>315</v>
+      </c>
+      <c r="O26" t="s">
+        <v>375</v>
+      </c>
+      <c r="P26" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>0.006603630573653749</v>
+      </c>
+      <c r="D27">
+        <v>0.003727283328771591</v>
+      </c>
+      <c r="E27">
+        <v>0.03271837905049324</v>
+      </c>
+      <c r="F27">
+        <v>0.001847955049015582</v>
+      </c>
+      <c r="G27">
+        <v>0.001833973685279489</v>
+      </c>
+      <c r="H27">
+        <v>1.001046839439227</v>
+      </c>
+      <c r="I27">
+        <v>0.04920286419849645</v>
+      </c>
+      <c r="J27">
+        <v>0.1139201670885086</v>
+      </c>
+      <c r="K27">
+        <v>196414.9375</v>
+      </c>
+      <c r="L27">
+        <v>1.8726806640625</v>
+      </c>
+      <c r="M27">
+        <v>6.520374774932861</v>
+      </c>
+      <c r="N27" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" t="s">
+        <v>376</v>
+      </c>
+      <c r="P27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>0.01618386136099959</v>
+      </c>
+      <c r="D28">
+        <v>0.008939472958445549</v>
+      </c>
+      <c r="E28">
+        <v>0.07581518590450287</v>
+      </c>
+      <c r="F28">
+        <v>0.002110594883561134</v>
+      </c>
+      <c r="G28">
+        <v>0.002217975212261081</v>
+      </c>
+      <c r="H28">
+        <v>1.001517106177288</v>
+      </c>
+      <c r="I28">
+        <v>0.04958946980144487</v>
+      </c>
+      <c r="J28">
+        <v>0.1179113760590553</v>
+      </c>
+      <c r="K28">
+        <v>4593630052352</v>
+      </c>
+      <c r="L28">
+        <v>4.33938455581665</v>
+      </c>
+      <c r="M28">
+        <v>6.748816967010498</v>
+      </c>
+      <c r="N28" t="s">
+        <v>317</v>
+      </c>
+      <c r="O28" t="s">
+        <v>377</v>
+      </c>
+      <c r="P28" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29">
+        <v>0.03233036512125879</v>
+      </c>
+      <c r="D29">
+        <v>0.01734721846878529</v>
+      </c>
+      <c r="E29">
+        <v>0.1464035362005234</v>
+      </c>
+      <c r="F29">
+        <v>0.002216792665421963</v>
+      </c>
+      <c r="G29">
+        <v>0.0024387261364609</v>
+      </c>
+      <c r="H29">
+        <v>1.001894243215206</v>
+      </c>
+      <c r="I29">
+        <v>0.05010643744695638</v>
+      </c>
+      <c r="J29">
+        <v>0.1184890642762184</v>
+      </c>
+      <c r="K29">
+        <v>2.94512155438675E+24</v>
+      </c>
+      <c r="L29">
+        <v>8.379604339599609</v>
+      </c>
+      <c r="M29">
+        <v>6.781881809234619</v>
+      </c>
+      <c r="N29" t="s">
+        <v>318</v>
+      </c>
+      <c r="O29" t="s">
+        <v>378</v>
+      </c>
+      <c r="P29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30">
+        <v>0.0797871860715909</v>
+      </c>
+      <c r="D30">
+        <v>0.04201633110642433</v>
+      </c>
+      <c r="E30">
+        <v>0.3509844243526459</v>
+      </c>
+      <c r="F30">
+        <v>0.002362926490604877</v>
+      </c>
+      <c r="G30">
+        <v>0.002711793407797813</v>
+      </c>
+      <c r="H30">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I30">
+        <v>0.05575669690240725</v>
+      </c>
+      <c r="J30">
+        <v>0.1197099611163139</v>
+      </c>
+      <c r="K30" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30">
+        <v>20.08906745910645</v>
+      </c>
+      <c r="M30">
+        <v>6.851761341094971</v>
+      </c>
+      <c r="N30" t="s">
+        <v>319</v>
+      </c>
+      <c r="O30" t="s">
+        <v>379</v>
+      </c>
+      <c r="P30" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31">
+        <v>0.1636007009233802</v>
+      </c>
+      <c r="D31">
+        <v>0.08498748391866684</v>
+      </c>
+      <c r="E31">
+        <v>0.7612921595573425</v>
+      </c>
+      <c r="F31">
+        <v>0.002474026056006551</v>
+      </c>
+      <c r="G31">
+        <v>0.003000563476234674</v>
+      </c>
+      <c r="H31">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I31">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J31">
+        <v>0.111635833978653</v>
+      </c>
+      <c r="K31" t="s">
+        <v>110</v>
+      </c>
+      <c r="L31">
+        <v>43.57358551025391</v>
+      </c>
+      <c r="M31">
+        <v>6.389627933502197</v>
+      </c>
+      <c r="N31" t="s">
+        <v>320</v>
+      </c>
+      <c r="O31" t="s">
+        <v>380</v>
+      </c>
+      <c r="P31" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32">
+        <v>0.0004234591388073488</v>
+      </c>
+      <c r="D32">
+        <v>-8.198698196792975E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.002978185191750526</v>
+      </c>
+      <c r="F32">
+        <v>0.0008691986440680921</v>
+      </c>
+      <c r="G32">
+        <v>0.0009396321256645024</v>
+      </c>
+      <c r="H32">
+        <v>1.000136331710958</v>
+      </c>
+      <c r="I32">
+        <v>0.0493425504083429</v>
+      </c>
+      <c r="J32">
+        <v>-0.02752917446196079</v>
+      </c>
+      <c r="K32">
+        <v>-0.2356239557266235</v>
+      </c>
+      <c r="L32">
+        <v>0.1704604476690292</v>
+      </c>
+      <c r="M32">
+        <v>-1.575669527053833</v>
+      </c>
+      <c r="N32" t="s">
+        <v>321</v>
+      </c>
+      <c r="O32" t="s">
+        <v>381</v>
+      </c>
+      <c r="P32" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <v>0.0005593551921238842</v>
+      </c>
+      <c r="D33">
+        <v>0.0001361024333164096</v>
+      </c>
+      <c r="E33">
+        <v>0.003863861318677664</v>
+      </c>
+      <c r="F33">
+        <v>0.0009951096726581454</v>
+      </c>
+      <c r="G33">
+        <v>0.001010947860777378</v>
+      </c>
+      <c r="H33">
+        <v>1.000239840926305</v>
+      </c>
+      <c r="I33">
+        <v>0.04933459616398567</v>
+      </c>
+      <c r="J33">
+        <v>0.03522446006536484</v>
+      </c>
+      <c r="K33">
+        <v>0.5619803667068481</v>
+      </c>
+      <c r="L33">
+        <v>0.2211533188819885</v>
+      </c>
+      <c r="M33">
+        <v>2.016119480133057</v>
+      </c>
+      <c r="N33" t="s">
+        <v>322</v>
+      </c>
+      <c r="O33" t="s">
+        <v>382</v>
+      </c>
+      <c r="P33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34">
+        <v>0.0006918662630949664</v>
+      </c>
+      <c r="D34">
+        <v>0.0002950167108792812</v>
+      </c>
+      <c r="E34">
+        <v>0.004671313799917698</v>
+      </c>
+      <c r="F34">
+        <v>0.001113052130676806</v>
+      </c>
+      <c r="G34">
+        <v>0.00109970651101321</v>
+      </c>
+      <c r="H34">
+        <v>1.000284304131822</v>
+      </c>
+      <c r="I34">
+        <v>0.04941150741622409</v>
+      </c>
+      <c r="J34">
+        <v>0.06315497308969498</v>
+      </c>
+      <c r="K34">
+        <v>1.628513097763062</v>
+      </c>
+      <c r="L34">
+        <v>0.2673689424991608</v>
+      </c>
+      <c r="M34">
+        <v>3.614760160446167</v>
+      </c>
+      <c r="N34" t="s">
+        <v>323</v>
+      </c>
+      <c r="O34" t="s">
+        <v>383</v>
+      </c>
+      <c r="P34" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>0.001327461545519133</v>
+      </c>
+      <c r="D35">
+        <v>0.0008734238217584789</v>
+      </c>
+      <c r="E35">
+        <v>0.009141616523265839</v>
+      </c>
+      <c r="F35">
+        <v>0.001394432038068771</v>
+      </c>
+      <c r="G35">
+        <v>0.001318100374191999</v>
+      </c>
+      <c r="H35">
+        <v>1.000371620466351</v>
+      </c>
+      <c r="I35">
+        <v>0.04958616823285872</v>
+      </c>
+      <c r="J35">
+        <v>0.09554369747638702</v>
+      </c>
+      <c r="K35">
+        <v>16.46435165405273</v>
+      </c>
+      <c r="L35">
+        <v>0.5232327580451965</v>
+      </c>
+      <c r="M35">
+        <v>5.468572616577148</v>
+      </c>
+      <c r="N35" t="s">
+        <v>324</v>
+      </c>
+      <c r="O35" t="s">
+        <v>384</v>
+      </c>
+      <c r="P35" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36">
+        <v>0.002548352351051051</v>
+      </c>
+      <c r="D36">
+        <v>0.001754962140694261</v>
+      </c>
+      <c r="E36">
+        <v>0.01819338276982307</v>
+      </c>
+      <c r="F36">
+        <v>0.001638331450521946</v>
+      </c>
+      <c r="G36">
+        <v>0.001602801377885044</v>
+      </c>
+      <c r="H36">
+        <v>1.000547339895525</v>
+      </c>
+      <c r="I36">
+        <v>0.04967004481246132</v>
+      </c>
+      <c r="J36">
+        <v>0.09646156430244446</v>
+      </c>
+      <c r="K36">
+        <v>311.416748046875</v>
+      </c>
+      <c r="L36">
+        <v>1.041322827339172</v>
+      </c>
+      <c r="M36">
+        <v>5.521108150482178</v>
+      </c>
+      <c r="N36" t="s">
+        <v>325</v>
+      </c>
+      <c r="O36" t="s">
+        <v>385</v>
+      </c>
+      <c r="P36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37">
+        <v>0.004933851828382592</v>
+      </c>
+      <c r="D37">
+        <v>0.003413469763472676</v>
+      </c>
+      <c r="E37">
+        <v>0.03804673627018929</v>
+      </c>
+      <c r="F37">
+        <v>0.001891547464765608</v>
+      </c>
+      <c r="G37">
+        <v>0.001898584538139403</v>
+      </c>
+      <c r="H37">
+        <v>1.000957578506865</v>
+      </c>
+      <c r="I37">
+        <v>0.04926453145462718</v>
+      </c>
+      <c r="J37">
+        <v>0.0897178053855896</v>
+      </c>
+      <c r="K37">
+        <v>70500.09375</v>
+      </c>
+      <c r="L37">
+        <v>2.177656412124634</v>
+      </c>
+      <c r="M37">
+        <v>5.135119915008545</v>
+      </c>
+      <c r="N37" t="s">
+        <v>326</v>
+      </c>
+      <c r="O37" t="s">
+        <v>386</v>
+      </c>
+      <c r="P37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38">
+        <v>0.01200078177315734</v>
+      </c>
+      <c r="D38">
+        <v>0.007873374037444592</v>
+      </c>
+      <c r="E38">
+        <v>0.09040196239948273</v>
+      </c>
+      <c r="F38">
+        <v>0.002119585871696472</v>
+      </c>
+      <c r="G38">
+        <v>0.002259298926219344</v>
+      </c>
+      <c r="H38">
+        <v>1.001480255656448</v>
+      </c>
+      <c r="I38">
+        <v>0.04967367480623777</v>
+      </c>
+      <c r="J38">
+        <v>0.08709295839071274</v>
+      </c>
+      <c r="K38">
+        <v>143887810560</v>
+      </c>
+      <c r="L38">
+        <v>5.174278259277344</v>
+      </c>
+      <c r="M38">
+        <v>4.984883308410645</v>
+      </c>
+      <c r="N38" t="s">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s">
+        <v>387</v>
+      </c>
+      <c r="P38" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39">
+        <v>0.0237255237628454</v>
+      </c>
+      <c r="D39">
+        <v>0.01542010903358459</v>
+      </c>
+      <c r="E39">
+        <v>0.1844597160816193</v>
+      </c>
+      <c r="F39">
+        <v>0.002222305396571755</v>
+      </c>
+      <c r="G39">
+        <v>0.002460032934322953</v>
+      </c>
+      <c r="H39">
+        <v>1.001889850905847</v>
+      </c>
+      <c r="I39">
+        <v>0.05005604276662981</v>
+      </c>
+      <c r="J39">
+        <v>0.08359608054161072</v>
+      </c>
+      <c r="K39">
+        <v>5.908364111989761E+21</v>
+      </c>
+      <c r="L39">
+        <v>10.55780124664307</v>
+      </c>
+      <c r="M39">
+        <v>4.784734725952148</v>
+      </c>
+      <c r="N39" t="s">
+        <v>328</v>
+      </c>
+      <c r="O39" t="s">
+        <v>388</v>
+      </c>
+      <c r="P39" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40">
+        <v>0.05852363238657854</v>
+      </c>
+      <c r="D40">
+        <v>0.0373946838080883</v>
+      </c>
+      <c r="E40">
+        <v>0.4510972499847412</v>
+      </c>
+      <c r="F40">
+        <v>0.002349034883081913</v>
+      </c>
+      <c r="G40">
+        <v>0.002730445237830281</v>
+      </c>
+      <c r="H40">
+        <v>1.002602524634348</v>
+      </c>
+      <c r="I40">
+        <v>0.05579382251179136</v>
+      </c>
+      <c r="J40">
+        <v>0.08289716392755508</v>
+      </c>
+      <c r="K40" t="s">
+        <v>110</v>
+      </c>
+      <c r="L40">
+        <v>25.81916046142578</v>
+      </c>
+      <c r="M40">
+        <v>4.744730949401855</v>
+      </c>
+      <c r="N40" t="s">
+        <v>329</v>
+      </c>
+      <c r="O40" t="s">
+        <v>389</v>
+      </c>
+      <c r="P40" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41">
+        <v>0.1211395693505156</v>
+      </c>
+      <c r="D41">
+        <v>0.07661543786525726</v>
+      </c>
+      <c r="E41">
+        <v>0.9785485863685608</v>
+      </c>
+      <c r="F41">
+        <v>0.002487879013642669</v>
+      </c>
+      <c r="G41">
+        <v>0.003023788798600435</v>
+      </c>
+      <c r="H41">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I41">
+        <v>0.06517124542314266</v>
+      </c>
+      <c r="J41">
+        <v>0.07829497754573822</v>
+      </c>
+      <c r="K41" t="s">
+        <v>110</v>
+      </c>
+      <c r="L41">
+        <v>56.00854873657227</v>
+      </c>
+      <c r="M41">
+        <v>4.481318950653076</v>
+      </c>
+      <c r="N41" t="s">
+        <v>330</v>
+      </c>
+      <c r="O41" t="s">
+        <v>390</v>
+      </c>
+      <c r="P41" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42">
+        <v>0.0001412155675377781</v>
+      </c>
+      <c r="D42">
+        <v>-0.0001729211071506143</v>
+      </c>
+      <c r="E42">
+        <v>0.002525778720155358</v>
+      </c>
+      <c r="F42">
+        <v>0.0009553626296110451</v>
+      </c>
+      <c r="G42">
+        <v>0.0009868604829534888</v>
+      </c>
+      <c r="H42">
+        <v>0.9998520602182478</v>
+      </c>
+      <c r="I42">
+        <v>0.04952100388309345</v>
+      </c>
+      <c r="J42">
+        <v>-0.06846249103546143</v>
+      </c>
+      <c r="K42">
+        <v>-0.4324986934661865</v>
+      </c>
+      <c r="L42">
+        <v>0.1445663571357727</v>
+      </c>
+      <c r="M42">
+        <v>-3.918543100357056</v>
+      </c>
+      <c r="N42" t="s">
+        <v>331</v>
+      </c>
+      <c r="O42" t="s">
+        <v>391</v>
+      </c>
+      <c r="P42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43">
+        <v>0.0001793766279859033</v>
+      </c>
+      <c r="D43">
+        <v>-0.0001049063794198446</v>
+      </c>
+      <c r="E43">
+        <v>0.003414194332435727</v>
+      </c>
+      <c r="F43">
+        <v>0.001093670376576483</v>
+      </c>
+      <c r="G43">
+        <v>0.00107190350536257</v>
+      </c>
+      <c r="H43">
+        <v>0.9998865345744462</v>
+      </c>
+      <c r="I43">
+        <v>0.04966583425813253</v>
+      </c>
+      <c r="J43">
+        <v>-0.03072654083371162</v>
+      </c>
+      <c r="K43">
+        <v>-0.2908470630645752</v>
+      </c>
+      <c r="L43">
+        <v>0.1954160183668137</v>
+      </c>
+      <c r="M43">
+        <v>-1.758675098419189</v>
+      </c>
+      <c r="N43" t="s">
+        <v>332</v>
+      </c>
+      <c r="O43" t="s">
+        <v>392</v>
+      </c>
+      <c r="P43" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44">
+        <v>0.000213254206971737</v>
+      </c>
+      <c r="D44">
+        <v>4.978736615157686E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.002384273568168283</v>
+      </c>
+      <c r="F44">
+        <v>0.001192943542264402</v>
+      </c>
+      <c r="G44">
+        <v>0.001153309596702456</v>
+      </c>
+      <c r="H44">
+        <v>0.9998919087247817</v>
+      </c>
+      <c r="I44">
+        <v>0.04978313708656049</v>
+      </c>
+      <c r="J44">
+        <v>0.02088156528770924</v>
+      </c>
+      <c r="K44">
+        <v>0.1773160696029663</v>
+      </c>
+      <c r="L44">
+        <v>0.1364671140909195</v>
+      </c>
+      <c r="M44">
+        <v>1.195184588432312</v>
+      </c>
+      <c r="N44" t="s">
+        <v>333</v>
+      </c>
+      <c r="O44" t="s">
+        <v>393</v>
+      </c>
+      <c r="P44" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45">
+        <v>0.0003502142488793799</v>
+      </c>
+      <c r="D45">
+        <v>0.0003582059871405363</v>
+      </c>
+      <c r="E45">
+        <v>0.001411017146892846</v>
+      </c>
+      <c r="F45">
+        <v>0.001442382577806711</v>
+      </c>
+      <c r="G45">
+        <v>0.001377933076582849</v>
+      </c>
+      <c r="H45">
+        <v>1.000046385845773</v>
+      </c>
+      <c r="I45">
+        <v>0.04991660702900837</v>
+      </c>
+      <c r="J45">
+        <v>0.253863662481308</v>
+      </c>
+      <c r="K45">
+        <v>2.232744216918945</v>
+      </c>
+      <c r="L45">
+        <v>0.08076146990060806</v>
+      </c>
+      <c r="M45">
+        <v>14.53022956848145</v>
+      </c>
+      <c r="N45" t="s">
+        <v>334</v>
+      </c>
+      <c r="O45" t="s">
+        <v>394</v>
+      </c>
+      <c r="P45" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46">
+        <v>0.0005692257756373833</v>
+      </c>
+      <c r="D46">
+        <v>0.0005772886797785759</v>
+      </c>
+      <c r="E46">
+        <v>0.002348814392462373</v>
+      </c>
+      <c r="F46">
+        <v>0.001700464868918061</v>
+      </c>
+      <c r="G46">
+        <v>0.001664956798776984</v>
+      </c>
+      <c r="H46">
+        <v>1.000365498620229</v>
+      </c>
+      <c r="I46">
+        <v>0.04993178587032784</v>
+      </c>
+      <c r="J46">
+        <v>0.2457787543535233</v>
+      </c>
+      <c r="K46">
+        <v>5.624595165252686</v>
+      </c>
+      <c r="L46">
+        <v>0.1344375610351562</v>
+      </c>
+      <c r="M46">
+        <v>14.06747913360596</v>
+      </c>
+      <c r="N46" t="s">
+        <v>335</v>
+      </c>
+      <c r="O46" t="s">
+        <v>395</v>
+      </c>
+      <c r="P46" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47">
+        <v>0.000948652502260386</v>
+      </c>
+      <c r="D47">
+        <v>0.0008609855431132019</v>
+      </c>
+      <c r="E47">
+        <v>0.004296457394957542</v>
+      </c>
+      <c r="F47">
+        <v>0.001919069327414036</v>
+      </c>
+      <c r="G47">
+        <v>0.001974375220015645</v>
+      </c>
+      <c r="H47">
+        <v>1.00072497445435</v>
+      </c>
+      <c r="I47">
+        <v>0.04939941032240381</v>
+      </c>
+      <c r="J47">
+        <v>0.2003942877054214</v>
+      </c>
+      <c r="K47">
+        <v>15.7632942199707</v>
+      </c>
+      <c r="L47">
+        <v>0.2459135502576828</v>
+      </c>
+      <c r="M47">
+        <v>11.46983814239502</v>
+      </c>
+      <c r="N47" t="s">
+        <v>336</v>
+      </c>
+      <c r="O47" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48">
+        <v>0.001981477649657482</v>
+      </c>
+      <c r="D48">
+        <v>0.001468570670112967</v>
+      </c>
+      <c r="E48">
+        <v>0.01029899716377258</v>
+      </c>
+      <c r="F48">
+        <v>0.002120237564668059</v>
+      </c>
+      <c r="G48">
+        <v>0.002327251015231013</v>
+      </c>
+      <c r="H48">
+        <v>1.001567528095384</v>
+      </c>
+      <c r="I48">
+        <v>0.04961756640202365</v>
+      </c>
+      <c r="J48">
+        <v>0.1425935626029968</v>
+      </c>
+      <c r="K48">
+        <v>121.4135971069336</v>
+      </c>
+      <c r="L48">
+        <v>0.589477002620697</v>
+      </c>
+      <c r="M48">
+        <v>8.161535263061523</v>
+      </c>
+      <c r="N48" t="s">
+        <v>337</v>
+      </c>
+      <c r="O48" t="s">
+        <v>397</v>
+      </c>
+      <c r="P48" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49">
+        <v>0.003597220185686517</v>
+      </c>
+      <c r="D49">
+        <v>0.002386771142482758</v>
+      </c>
+      <c r="E49">
+        <v>0.01997169852256775</v>
+      </c>
+      <c r="F49">
+        <v>0.002231512451544404</v>
+      </c>
+      <c r="G49">
+        <v>0.002516361884772778</v>
+      </c>
+      <c r="H49">
+        <v>1.001875365196894</v>
+      </c>
+      <c r="I49">
+        <v>0.0502537630439346</v>
+      </c>
+      <c r="J49">
+        <v>0.1195076704025269</v>
+      </c>
+      <c r="K49">
+        <v>2463.80419921875</v>
+      </c>
+      <c r="L49">
+        <v>1.143107175827026</v>
+      </c>
+      <c r="M49">
+        <v>6.840182781219482</v>
+      </c>
+      <c r="N49" t="s">
+        <v>338</v>
+      </c>
+      <c r="O49" t="s">
+        <v>398</v>
+      </c>
+      <c r="P49" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50">
+        <v>0.008679435446614026</v>
+      </c>
+      <c r="D50">
+        <v>0.005128358025103807</v>
+      </c>
+      <c r="E50">
+        <v>0.05131400376558304</v>
+      </c>
+      <c r="F50">
+        <v>0.002361893421038985</v>
+      </c>
+      <c r="G50">
+        <v>0.002778565045446157</v>
+      </c>
+      <c r="H50">
+        <v>1.002670524090353</v>
+      </c>
+      <c r="I50">
+        <v>0.05582449286615769</v>
+      </c>
+      <c r="J50">
+        <v>0.0999407097697258</v>
+      </c>
+      <c r="K50">
+        <v>18956388</v>
+      </c>
+      <c r="L50">
+        <v>2.937026262283325</v>
+      </c>
+      <c r="M50">
+        <v>5.720241546630859</v>
+      </c>
+      <c r="N50" t="s">
+        <v>339</v>
+      </c>
+      <c r="O50" t="s">
+        <v>399</v>
+      </c>
+      <c r="P50" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51">
+        <v>0.01639269987139668</v>
+      </c>
+      <c r="D51">
+        <v>0.009229474700987339</v>
+      </c>
+      <c r="E51">
+        <v>0.09445172548294067</v>
+      </c>
+      <c r="F51">
+        <v>0.002458399860188365</v>
+      </c>
+      <c r="G51">
+        <v>0.003014946589246392</v>
+      </c>
+      <c r="H51">
+        <v>1.003671970624235</v>
+      </c>
+      <c r="I51">
+        <v>0.06535901646999488</v>
+      </c>
+      <c r="J51">
+        <v>0.0977163165807724</v>
+      </c>
+      <c r="K51">
+        <v>11773935616000</v>
+      </c>
+      <c r="L51">
+        <v>5.40607213973999</v>
+      </c>
+      <c r="M51">
+        <v>5.592925548553467</v>
+      </c>
+      <c r="N51" t="s">
+        <v>340</v>
+      </c>
+      <c r="O51" t="s">
+        <v>400</v>
+      </c>
+      <c r="P51" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52">
+        <v>0.0001554775011728714</v>
+      </c>
+      <c r="D52">
+        <v>0.0002456518122926354</v>
+      </c>
+      <c r="E52">
+        <v>0.0006786643643863499</v>
+      </c>
+      <c r="F52">
+        <v>0.001073517720215023</v>
+      </c>
+      <c r="G52">
+        <v>0.001079695532098413</v>
+      </c>
+      <c r="H52">
+        <v>0.9992433441851345</v>
+      </c>
+      <c r="I52">
+        <v>0.05000667185208931</v>
+      </c>
+      <c r="J52">
+        <v>0.3619636297225952</v>
+      </c>
+      <c r="K52">
+        <v>1.236210584640503</v>
+      </c>
+      <c r="L52">
+        <v>0.0388442724943161</v>
+      </c>
+      <c r="M52">
+        <v>20.71747779846191</v>
+      </c>
+      <c r="N52" t="s">
+        <v>341</v>
+      </c>
+      <c r="O52" t="s">
+        <v>401</v>
+      </c>
+      <c r="P52" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53">
+        <v>0.0001856071184383586</v>
+      </c>
+      <c r="D53">
+        <v>0.0002956627286039293</v>
+      </c>
+      <c r="E53">
+        <v>0.0007492808508686721</v>
+      </c>
+      <c r="F53">
+        <v>0.00114015000872314</v>
+      </c>
+      <c r="G53">
+        <v>0.001134276972152293</v>
+      </c>
+      <c r="H53">
+        <v>0.9991717872103019</v>
+      </c>
+      <c r="I53">
+        <v>0.05025876636265565</v>
+      </c>
+      <c r="J53">
+        <v>0.3945953249931335</v>
+      </c>
+      <c r="K53">
+        <v>1.633649110794067</v>
+      </c>
+      <c r="L53">
+        <v>0.04288610070943832</v>
+      </c>
+      <c r="M53">
+        <v>22.58519744873047</v>
+      </c>
+      <c r="N53" t="s">
+        <v>342</v>
+      </c>
+      <c r="O53" t="s">
+        <v>402</v>
+      </c>
+      <c r="P53" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54">
+        <v>0.0002091339542476236</v>
+      </c>
+      <c r="D54">
+        <v>0.0003327947633806616</v>
+      </c>
+      <c r="E54">
+        <v>0.0007964756223373115</v>
+      </c>
+      <c r="F54">
+        <v>0.001200274215079844</v>
+      </c>
+      <c r="G54">
+        <v>0.00116891146171838</v>
+      </c>
+      <c r="H54">
+        <v>0.9991517689226213</v>
+      </c>
+      <c r="I54">
+        <v>0.05046131316901636</v>
+      </c>
+      <c r="J54">
+        <v>0.4178342223167419</v>
+      </c>
+      <c r="K54">
+        <v>1.974801540374756</v>
+      </c>
+      <c r="L54">
+        <v>0.04558735713362694</v>
+      </c>
+      <c r="M54">
+        <v>23.91530609130859</v>
+      </c>
+      <c r="N54" t="s">
+        <v>343</v>
+      </c>
+      <c r="O54" t="s">
+        <v>403</v>
+      </c>
+      <c r="P54" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55">
+        <v>0.000285771930906634</v>
+      </c>
+      <c r="D55">
+        <v>0.0004489909333642572</v>
+      </c>
+      <c r="E55">
+        <v>0.0009497373248450458</v>
+      </c>
+      <c r="F55">
+        <v>0.001406731083989143</v>
+      </c>
+      <c r="G55">
+        <v>0.001392096630297601</v>
+      </c>
+      <c r="H55">
+        <v>0.9993307242969155</v>
+      </c>
+      <c r="I55">
+        <v>0.0506794281902102</v>
+      </c>
+      <c r="J55">
+        <v>0.4727527499198914</v>
+      </c>
+      <c r="K55">
+        <v>3.350995063781738</v>
+      </c>
+      <c r="L55">
+        <v>0.05435949936509132</v>
+      </c>
+      <c r="M55">
+        <v>27.05864143371582</v>
+      </c>
+      <c r="N55" t="s">
+        <v>344</v>
+      </c>
+      <c r="O55" t="s">
+        <v>404</v>
+      </c>
+      <c r="P55" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56">
+        <v>0.0003669855032808074</v>
+      </c>
+      <c r="D56">
+        <v>0.0005518777179531753</v>
+      </c>
+      <c r="E56">
+        <v>0.00110836757812649</v>
+      </c>
+      <c r="F56">
+        <v>0.001658244407735765</v>
+      </c>
+      <c r="G56">
+        <v>0.001743341446854174</v>
+      </c>
+      <c r="H56">
+        <v>0.9997586128956429</v>
+      </c>
+      <c r="I56">
+        <v>0.05056263634385581</v>
+      </c>
+      <c r="J56">
+        <v>0.4979194104671478</v>
+      </c>
+      <c r="K56">
+        <v>5.093746662139893</v>
+      </c>
+      <c r="L56">
+        <v>0.06343891471624374</v>
+      </c>
+      <c r="M56">
+        <v>28.49909019470215</v>
+      </c>
+      <c r="N56" t="s">
+        <v>345</v>
+      </c>
+      <c r="O56" t="s">
+        <v>405</v>
+      </c>
+      <c r="P56" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57">
+        <v>0.0004452449152877072</v>
+      </c>
+      <c r="D57">
+        <v>0.0006314408383332193</v>
+      </c>
+      <c r="E57">
+        <v>0.001330910250544548</v>
+      </c>
+      <c r="F57">
+        <v>0.001801379024982452</v>
+      </c>
+      <c r="G57">
+        <v>0.001990538090467453</v>
+      </c>
+      <c r="H57">
+        <v>1.000593103459366</v>
+      </c>
+      <c r="I57">
+        <v>0.04930217268807154</v>
+      </c>
+      <c r="J57">
+        <v>0.4744428396224976</v>
+      </c>
+      <c r="K57">
+        <v>6.908851623535156</v>
+      </c>
+      <c r="L57">
+        <v>0.07617644965648651</v>
+      </c>
+      <c r="M57">
+        <v>27.15537643432617</v>
+      </c>
+      <c r="N57" t="s">
+        <v>346</v>
+      </c>
+      <c r="O57" t="s">
+        <v>406</v>
+      </c>
+      <c r="P57" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58">
+        <v>0.0005375709232285506</v>
+      </c>
+      <c r="D58">
+        <v>0.0007495718309655786</v>
+      </c>
+      <c r="E58">
+        <v>0.001833642832934856</v>
+      </c>
+      <c r="F58">
+        <v>0.001982163870707154</v>
+      </c>
+      <c r="G58">
+        <v>0.002335313707590103</v>
+      </c>
+      <c r="H58">
+        <v>1.001150403462369</v>
+      </c>
+      <c r="I58">
+        <v>0.05000752183965073</v>
+      </c>
+      <c r="J58">
+        <v>0.4087883532047272</v>
+      </c>
+      <c r="K58">
+        <v>10.64329433441162</v>
+      </c>
+      <c r="L58">
+        <v>0.104951024055481</v>
+      </c>
+      <c r="M58">
+        <v>23.39755439758301</v>
+      </c>
+      <c r="N58" t="s">
+        <v>347</v>
+      </c>
+      <c r="O58" t="s">
+        <v>407</v>
+      </c>
+      <c r="P58" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59">
+        <v>0.0005997418584626421</v>
+      </c>
+      <c r="D59">
+        <v>0.0008429386653006077</v>
+      </c>
+      <c r="E59">
+        <v>0.002382162492722273</v>
+      </c>
+      <c r="F59">
+        <v>0.00203491747379303</v>
+      </c>
+      <c r="G59">
+        <v>0.002557917730882764</v>
+      </c>
+      <c r="H59">
+        <v>1.00124829333689</v>
+      </c>
+      <c r="I59">
+        <v>0.05074980961678765</v>
+      </c>
+      <c r="J59">
+        <v>0.3538543879985809</v>
+      </c>
+      <c r="K59">
+        <v>14.80413818359375</v>
+      </c>
+      <c r="L59">
+        <v>0.1363462954759598</v>
+      </c>
+      <c r="M59">
+        <v>20.25333404541016</v>
+      </c>
+      <c r="N59" t="s">
+        <v>348</v>
+      </c>
+      <c r="O59" t="s">
+        <v>408</v>
+      </c>
+      <c r="P59" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60">
+        <v>0.0006746876762316604</v>
+      </c>
+      <c r="D60">
+        <v>0.001004855032078922</v>
+      </c>
+      <c r="E60">
+        <v>0.003754102159291506</v>
+      </c>
+      <c r="F60">
+        <v>0.002070471178740263</v>
+      </c>
+      <c r="G60">
+        <v>0.002776089822873473</v>
+      </c>
+      <c r="H60">
+        <v>1.002257427395126</v>
+      </c>
+      <c r="I60">
+        <v>0.05631481516539293</v>
+      </c>
+      <c r="J60">
+        <v>0.2676685452461243</v>
+      </c>
+      <c r="K60">
+        <v>25.84612655639648</v>
+      </c>
+      <c r="L60">
+        <v>0.2148711085319519</v>
+      </c>
+      <c r="M60">
+        <v>15.3203706741333</v>
+      </c>
+      <c r="N60" t="s">
+        <v>349</v>
+      </c>
+      <c r="O60" t="s">
+        <v>409</v>
+      </c>
+      <c r="P60" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61">
+        <v>0.0007249681352620064</v>
+      </c>
+      <c r="D61">
+        <v>0.001077146851457655</v>
+      </c>
+      <c r="E61">
+        <v>0.005085800774395466</v>
+      </c>
+      <c r="F61">
+        <v>0.002092809183523059</v>
+      </c>
+      <c r="G61">
+        <v>0.002917692996561527</v>
+      </c>
+      <c r="H61">
+        <v>1.003335373317013</v>
+      </c>
+      <c r="I61">
+        <v>0.06582658500346944</v>
+      </c>
+      <c r="J61">
+        <v>0.2117949426174164</v>
+      </c>
+      <c r="K61">
+        <v>33.01924896240234</v>
+      </c>
+      <c r="L61">
+        <v>0.2910926640033722</v>
+      </c>
+      <c r="M61">
+        <v>12.12236976623535</v>
+      </c>
+      <c r="N61" t="s">
+        <v>350</v>
+      </c>
+      <c r="O61" t="s">
+        <v>410</v>
+      </c>
+      <c r="P61" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/ffn_noise/performance.xlsx
+++ b/scripts/ffn_noise/performance.xlsx
@@ -8919,12 +8919,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0003244758991058916</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>4.655863813241012E-05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0006909972289577127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>6.991143891355023E-05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0001550738379592076</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-0.0001250271307071671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0001672422949923202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0003024827165063471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0009447424090467393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0004071739967912436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>-0.0001659925328567624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.001780417980626225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.0002626177156344056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.0003368136531207711</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0003693788312375546</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-0.0001514915493316948</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-0.0007692816434428096</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.0009440213325433433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.000438487040810287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0003979190951213241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>-0.000208227225812152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.0008024725830182433</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.0006927663926035166</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0006602066569030285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.001583168283104897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0006440355791710317</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.0002613068500068039</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0001709774223854765</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.0001992499019252136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>9.757705993251875E-05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0001134507765527815</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0006053824326954782</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>3.863017627736554E-05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0002135466929757968</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.00060090800980106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.0001748626964399591</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.0005354578606784344</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0001484978274675086</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.0009027850464917719</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0007247520261444151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.0002129247441189364</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.000637748627923429</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-0.0008482733392156661</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.001107842428609729</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.0007403645431622863</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>9.977272566175088E-05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>-9.333551133750007E-05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0004707468615379184</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0002632231335155666</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>7.519579958170652E-05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>-5.977585169603117E-05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>5.171031079953536E-05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-0.0002061228296952322</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.0006943448097445071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.000138154297019355</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.000833509024232626</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>-0.0003602289070840925</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>5.181422238820232E-05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0004024835070595145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.0002141159784514457</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0001901577197713777</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>-3.241008380427957E-05</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0005460361135192215</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.001819070195779204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0004231629136484116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0002904665598180145</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.000230139383347705</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.0003902831231243908</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.0006422741571441293</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.0003341566189192235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>-4.927983900415711E-05</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.0006577497697435319</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0005186597118154168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.000927899032831192</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.001598215196281672</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.0006416293908841908</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.003161625238135457</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0005113953375257552</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>5.807490015286021E-05</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>0.000310044561047107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>0.0003609331615734845</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.0003001407603733242</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.0002544975432101637</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>-0.0001577276125317439</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>-8.883985719876364E-05</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>-0.0002545310708228499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0004581435641739517</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>-2.749311715888325E-05</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.0006297824438661337</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0003231103473808616</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>7.216350786620751E-05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>0.0001067994526238181</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0006233485182747245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.0008990980568341911</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>-0.0001658937981119379</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0002669272071216255</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0002667044172994792</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.0003150387201458216</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0001888947881525382</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>-0.0001514467876404524</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.0001907373516587541</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-4.452042412594892E-05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.0003082260373048484</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.0002222650364274159</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0002213667321484536</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.0008063131244853139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001235329313203692</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>-0.0001113530088332482</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0005088043981231749</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.0012975794961676</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.0001232722424902022</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>-0.0002132918598363176</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.0001062694718712009</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-3.448688221396878E-05</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>-2.266117735416628E-05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>-0.001134378835558891</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.000360923440894112</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.0002870222961064428</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>-9.28647059481591E-05</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>-0.000157877104356885</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0006192901055328548</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>-8.484497084282339E-05</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.000379091186914593</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0005471436306834221</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0001043213705997914</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.001796135678887367</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0004338566504884511</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0002522342838346958</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>0.0006712654139846563</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.0008810564177110791</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>0.0001657031534705311</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-0.0001857605675468221</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>0.0003073712287005037</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0003068857186008245</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0002321254723938182</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.0008548913756385446</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0002620479499455541</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>-0.000210653743124567</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0006893477984704077</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>0.0001349559606751427</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0006281865644268692</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.004885268863290548</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>-0.0002913088537752628</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.0004837198357563466</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.000221172085730359</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>7.713616651017219E-05</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.0008242038893513381</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.0005024707061238587</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.0002445020072627813</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0002952363574877381</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0002178110589738935</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.0003335961664561182</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>-6.370821938617155E-05</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.000658731849398464</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.002372212242335081</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0005741511704400182</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0002035394281847402</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.0009878515265882015</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0002649946254678071</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0002997859555762261</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0002920124388765544</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0002412845788057894</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0003121595946140587</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.0003655346517916769</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0001472303993068635</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.0007114766049198806</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>8.840295777190477E-05</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.001910076476633549</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.000428070779889822</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>5.093784056953155E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>0.0002260508626932278</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0004676923272199929</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.0003534443094395101</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>0.0001349781960016116</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0003311220789328218</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0003193161392118782</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.000139727329951711</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.000277610874036327</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.000474145170301199</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0004493824962992221</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>-0.0007027024403214455</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>1.642753886699211E-05</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>0.0002945569867733866</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>9.611483255866915E-05</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0002017965744016692</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.000208611148991622</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.0003483216278254986</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.001610755221918225</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0004840874171350151</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0001546880084788427</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.0004467737162485719</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0001362026087008417</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>0.001041104434989393</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>0.002656022785231471</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.000706099031958729</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>2.968498120026197E-05</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0006393799558281898</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0002445936552248895</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>0.0001497913763159886</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.00029783631907776</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>4.841855115955696E-05</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>-0.0001289620558964089</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.001338860834948719</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0003157706814818084</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>8.904674177756533E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0004428546235430986</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.001585400546900928</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>0.001173948752693832</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.001213774434290826</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.0003560076584108174</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>-1.61514944920782E-05</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0004301862209104002</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>1.745499321259558E-05</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>-0.0001182570922537707</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0001022320502670482</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0002504277508705854</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0004866844974458218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>0.0005596933769993484</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0002096488751703873</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.002439014380797744</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.0009011028450913727</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>0.0003984557406511158</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.000657496799249202</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0003385875897947699</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0005236560828052461</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.0002515660307835788</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>6.433526141336188E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0005056358058936894</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.001399150933139026</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0007142615504562855</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002639620797708631</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>0.0004095473559573293</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0003442811139393598</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0004770105588249862</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>6.267839489737526E-05</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0003990456752944738</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.00037058733869344</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>-0.000669769593514502</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>6.355714140227064E-05</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.001826221472583711</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001130525124608539</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>-4.534985055215657E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0004737301496788859</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>-2.922954445239156E-05</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>9.665787365520373E-05</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.00260668620467186</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0004784235206898302</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>5.771986616309732E-05</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0006303865229710937</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>9.59760945988819E-05</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0003507842484395951</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0003218764322809875</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>7.105251279426739E-05</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>0.000125106584164314</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>-0.0002915195364039391</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>0.0003740910324268043</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.000411173008615151</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.000148727820487693</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001510235131718218</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>2.624058197397972E-07</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.0001471676660003141</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>1.626622179173864E-05</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>7.839281170163304E-05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>-1.744078690535389E-05</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0002821141970343888</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.000107390180346556</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.0002677789016161114</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>-0.0004029081901535392</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>6.950827810214832E-05</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0002547231270000339</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.000169811348314397</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.001701633329503238</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0003409791679587215</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0002205071650678292</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>7.172134792199358E-05</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>-7.541533705079928E-05</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>3.400051809876459E-06</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0001703715388430282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.0001666895113885403</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0005151638761162758</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0004027539398521185</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0004884419031441212</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.0001644663570914418</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0007611528853885829</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.002944005653262138</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0007614995120093226</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.0004321722954045981</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0002151722874259576</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>0.0001004978184937499</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>-6.734468479407951E-05</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.0005910285981371999</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0003812524664681405</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>-0.0001217915050801821</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0007072833832353354</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0003320348332636058</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0004128306463826448</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0001910583960125223</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001486006192862988</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>0.0001027778853313066</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0003404846647754312</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>6.341119387798244E-06</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0004082869563717395</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0002494361542630941</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0001082739909179509</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0002274752187076956</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002453629858791828</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-4.310043368604966E-05</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.0006973232957534492</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0003748289600480348</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>0.000158744616783224</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0001420632179360837</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>-0.0002628976653795689</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.0008826670818962157</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.001021630712784827</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0006706964923068881</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0004219983238726854</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>-2.090164343826473E-05</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>0.0002206448407378048</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>-7.130447920644656E-05</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.0007979147485457361</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0002656769356690347</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-9.145677904598415E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0008942036074586213</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.00136990356259048</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>0.0006621420034207404</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.001048702746629715</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>-4.057204205309972E-05</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>-3.287324943812564E-05</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>-2.646617576829158E-05</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0001251764770131558</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001129689859226346</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.001173708122223616</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0006126567022874951</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.0005395042826421559</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004907151451334357</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001564508769661188</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.0005174807156436145</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.0004046207177452743</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>-0.0002308363618794829</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.000230856632697396</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.0005982415750622749</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>-4.3374649976613E-05</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.0003874057729262859</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.0008607343188486993</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>-7.723569410700293E-07</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0004290630749892443</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0001650779158808291</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0002902289561461657</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0006408239132724702</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.001160967396572232</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001316282083280385</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0008441275567747653</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0007138438522815704</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.001163641456514597</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.001155726495198905</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.0003476575657259673</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.000258555868640542</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>3.422256850171834E-05</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0006967929657548666</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.0004882256907876581</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>0.0002297147293575108</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.002398451557382941</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-0.0003772811323869973</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001461558626033366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>-0.0001602159609319642</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0009296235512010753</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.0002271456323796883</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.001060247304849327</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-0.0001258213160326704</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>0.0002228864468634129</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>-4.024790996481897E-06</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0004024821682833135</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.000349073059624061</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>-0.0001845914666773751</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.0006688403082080185</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.002955015283077955</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>0.0005053323693573475</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>0.0005973051302134991</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>1.046672579718688E-07</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0002830198791343719</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.0008109631598927081</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>6.678152431049966E-07</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0006211797008290887</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>5.213603435549885E-05</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>-0.00042691410635598</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.00140929501503706</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.001992137636989355</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001727001275867224</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.0009848033078014851</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>-0.0005074742366559803</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.0001620763505343348</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.0006324569112621248</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.001303566270507872</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.0004409593529999256</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>-0.0001600418909220025</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>-4.906611138721928E-06</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0002394520124653354</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>0.0002252174745080993</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>-0.0001431165146641433</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0002137834380846471</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>0.0003145014343317598</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>-0.0004693676310125738</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.0007553818286396563</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.0007776233251206577</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-9.849686466623098E-05</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.002497143344953656</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>-0.0004732946690637618</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-4.518946661846712E-05</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.0002835582999978215</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>4.968353096046485E-06</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>9.690995648270473E-05</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0002533298975322396</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0004010518314316869</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>0.001230824622325599</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>1.75941258930834E-05</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0003256192721892148</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>-2.913904245360754E-05</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0005392531165853143</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.000498429813887924</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0004851303237956017</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001619458897039294</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-0.0003462376189418137</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.001007268438115716</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.0003249028231948614</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001552245579659939</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0005071276682429016</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001393967075273395</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.0004874121223110706</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.001518521225079894</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>-0.0002737952163442969</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0002776247274596244</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0002629182708915323</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.001293544075451791</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0003950078971683979</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0004854222643189132</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0007150348974391818</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.001815283903852105</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>9.286955901188776E-05</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.0009326902800239623</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.002733964473009109</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>-0.0001382615009788424</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0004821130714844912</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0004520620277617127</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0007231474155560136</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>-0.0002528667391743511</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003364731674082577</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0003677374625112861</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>-2.690731525945012E-05</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.0002218057634308934</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>0.0002934698713943362</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>1.86726847459795E-05</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0007073745364323258</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001343557494692504</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0006660603685304523</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.001167170237749815</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0003408419725019485</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0007030711858533323</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0007511889562010765</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0003079400630667806</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001186698093079031</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.0004344865155871958</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.0005677007138729095</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0002396870986558497</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0002830396988429129</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.001312199048697948</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0005504407454282045</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001092749647796154</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0004721651785075665</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001099977642297745</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0003579088370315731</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>6.009567005094141E-05</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>-6.251729791983962E-05</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0003728421288542449</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0003361735725775361</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0002053842908935621</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0002294752048328519</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>-0.0002843594993464649</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.0005114388186484575</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.00503151910379529</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.001325625460594893</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>-0.0002664365456439555</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0005853220354765654</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>-5.207481808611192E-05</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0004290991637390107</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-0.0001984693517442793</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0003846733598038554</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>-0.0001112248064600863</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.0007101946393959224</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0004355059063527733</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.000114093920274172</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0003636774490587413</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.0002413627371424809</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0002800473594106734</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0008242962067015469</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>1.853785397543106E-05</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0005732794525101781</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>5.440623863250948E-05</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0002364862011745572</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>-8.524453733116388E-06</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.0005074871587567031</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0003519944730214775</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0008826228440739214</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001356145367026329</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.0003888634382747114</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>6.648933049291372E-05</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.001649934449233115</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0005036034854128957</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.0001792796392692253</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.00010526659025345</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>-2.139467505912762E-05</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0004271453944966197</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0005496255471371114</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.0002263061323901638</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>-0.000150325009599328</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>6.898925494169816E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>-0.0002746800309978426</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.001162174041382968</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.00045241360203363</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>-4.340033410699107E-05</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>4.493194137467071E-05</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0004681418649852276</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0001890140265459195</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0007418723544105887</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001695903483778238</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.0008222470059990883</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.001994501799345016</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>7.430186087731272E-05</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>4.209578037261963E-05</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.000600877043325454</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0006168291438370943</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0004225966986268759</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>-3.686190666485345E-06</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.0007552563911303878</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.0007271944195963442</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>0.0005633339751511812</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001484791864641011</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>-1.517899818281876E-05</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.003429383737966418</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>2.873185621865559E-05</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>-0.0001374392159050331</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0004840665496885777</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.000420470634708181</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>9.864350431598723E-05</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0001938203058671206</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0005261437618173659</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0002388128777965903</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.000922824430745095</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0007433726568706334</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.0004604757123161107</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0004616080841515213</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001840464072301984</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001417428953573108</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0001030097919283435</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0006328141316771507</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0006871653022244573</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0006618123734369874</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.0001955960324266925</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.001362451701425016</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.0004027945687994361</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.002027656650170684</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>0.001278051524423063</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>5.497981305779831E-07</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0007702666334807873</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>-0.005654007196426392</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.001416169106960297</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0007231049821712077</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0002638903388287872</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.0004672390350606292</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.00129787833429873</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>-0.001069309189915657</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0006739028031006455</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.0003960118920076638</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.001311295898631215</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.002787167672067881</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.0002741974894888699</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>-0.0001379264431307092</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.005011345725506544</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.001317887450568378</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>3.508596637402661E-05</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.001192510011605918</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001615246175788343</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0002137678966391832</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0006565998774021864</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0004408476816024631</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0004224787116982043</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>2.529166749809519E-06</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0009751825709827244</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.000233099315664731</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>-5.304520891513675E-05</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.0004589345189742744</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.001044850680045784</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.001053234096616507</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>-0.0001106601484934799</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0007299763965420425</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0005267235683277249</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.0009643220691941679</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>6.964348722249269E-05</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-6.647894042544067E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>-0.0004304031317587942</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001438968000002205</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.003358103800565004</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.001854538451880217</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.00886397622525692</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.00180446298327297</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0001466070534661412</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001305336132645607</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.002686328487470746</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.000268356961896643</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0001534076873213053</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0004703006125055254</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>8.315696322824806E-05</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0006447315099649131</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>0.0001776112476363778</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0006958958110772073</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>-7.243677828228101E-05</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-0.002236714120954275</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0003679898800328374</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-6.414240488084033E-06</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0003489774826448411</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.002075609052553773</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>0.001208910252898932</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.001180305145680904</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>-0.0008460140088573098</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.0002351217699469998</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>-0.0001408378448104486</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.0001742087333695963</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0003026649064850062</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0001891603751573712</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>-0.003031574422493577</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0008072455530054867</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001158842002041638</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.0002445292193442583</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.00114170229062438</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.001298738177865744</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>3.141717024846002E-05</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0005299134645611048</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0005740621127188206</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0005093561485409737</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.001390988822095096</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.001441959990188479</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0001628350146347657</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>0.00380641408264637</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0009808610193431377</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001003031618893147</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0008414021576754749</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>0.0001710068609099835</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>0.001760173821821809</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>0.0007114246836863458</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.001534221577458084</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>0.0001292934321099892</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.001173329306766391</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.0003998025495093316</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.003140054875984788</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.0001235598901985213</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.002177504356950521</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>0.0005990630597807467</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0005235778517089784</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.000216706219362095</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-2.646253233251628E-05</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003486563451588154</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.000991770182736218</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>0.0001894676825031638</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.0007946431287564337</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.002177384216338396</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.001387878553941846</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>-0.0009503384935669601</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.002611496951431036</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.004739530384540558</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.001095777610316873</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.0001737012935336679</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.000270970311248675</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>-0.000480948860058561</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0004362512554507703</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0003436381230130792</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>0.0005002295947633684</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0005575721152126789</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>0.0003001378790941089</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0005488057504408062</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>-8.144741627802432E-07</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>-0.0003266872954554856</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.005551998969167471</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>-0.000104215694591403</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.001564918318763375</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>8.380738290725276E-05</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.000792309467215091</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.000478772766655311</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>6.768570528947748E-06</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.000537456595338881</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>-0.0006673578754998744</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.001892009051516652</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>-0.0002295032754773274</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>0.0005630010273307562</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.0003703626280184835</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.0007178816013038158</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>0.0002797039633151144</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>-0.000159279050421901</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.0004262900329194963</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>-9.395822416990995E-05</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0006209363345988095</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>0.0001089775614673272</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>-0.0004779609444085509</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.001312353764660656</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0001292232482228428</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0004092108283657581</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.0009366011945530772</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>0.0005885475547984242</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>0.006909552495926619</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>-0.0008299907785840333</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.001290242536924779</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0001479888305766508</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>-0.0005562182632274926</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>3.035271765838843E-05</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>-0.0003072815015912056</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>0.0001820508914534003</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0004698991542682052</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>0.001281356555409729</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0004327462520450354</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>0.0003625783137977123</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>0.001620220369659364</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>-0.004851568955928087</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>0.0001938883360708132</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0002178039430873469</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>0.0004846778174396604</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>0.0006099238526076078</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>-0.0004780339368153363</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.001198242651298642</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0005709384568035603</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0008225612691603601</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>-0.0004685614549089223</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>0.000651274633128196</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0002591430675238371</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>-0.0006348906899802387</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.005383884999901056</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.001305945916101336</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.000457896530861035</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0003676861524581909</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.0003890294174198061</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0005316118476912379</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>-8.117329707602039E-05</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>9.018213313538581E-05</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>0.0001748304639477283</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.000486729433760047</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>-0.0001897119509521872</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0009022632148116827</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>-0.0004173866473138332</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.003112706122919917</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.002534455386921763</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001745569752529263</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.000550358381588012</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>0.0005620482843369246</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>-0.0002342653751838952</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0002365834661759436</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.0007141099194996059</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0006109311361797154</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0005907993181608617</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0006364238797686994</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0001342727919109166</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0006664845859631896</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.001687055686488748</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0006668847636319697</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>0.0001616057998035103</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>7.030340930214152E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0004852771235164255</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>-0.0001306666963500902</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0005719376495108008</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.00240434124134481</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0008402944076806307</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>-8.518856338923797E-05</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0003409475611988455</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0004160018288530409</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>-3.08665657939855E-05</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>6.436079274863005E-05</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0005893390043638647</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001296365866437554</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.001956307096406817</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-7.911655848147348E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.0002401079254923388</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>0.0001065298274625093</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.002365350257605314</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0005474949721246958</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0001279769785469398</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.001291988999582827</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0004371656395960599</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>-3.298128649475984E-05</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>1.047508476403891E-06</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0002956508542411029</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0004648245230782777</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>6.61565427435562E-05</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.0001468763366574422</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.000737025635316968</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.000383207545382902</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.003261025063693523</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>-4.305385300540365E-05</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0006907879142090678</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>3.220582220819779E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>0.0003450057120062411</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>-0.0005275422590784729</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>-4.841778718400747E-05</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>-0.0001774723641574383</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0006211733561940491</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>8.770707790972665E-05</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-0.0003452048695180565</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>-0.0002201461757067591</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.0007047289982438087</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>0.001554231392219663</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-0.0003455247788224369</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.00138314685318619</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0007797584985382855</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0003939664456993341</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0004519070207607001</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.001384975621476769</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0009539850289002061</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0004051625146530569</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.001222301740199327</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.000903697160538286</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0005712794954888523</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0004873820871580392</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.001090770121663809</v>
       </c>
     </row>
   </sheetData>
@@ -8934,12 +15478,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.004869937896728516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.005753755569458008</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.003428459167480469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.003386735916137695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.004722476005554199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.007275223731994629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.00224006175994873</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.003029942512512207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.002421855926513672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.00564873218536377</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.006531000137329102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.005434393882751465</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.006269335746765137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.002540230751037598</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.008414387702941895</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.003057122230529785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.001951217651367188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.00636589527130127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.005756735801696777</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.003811359405517578</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.002677440643310547</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.005080223083496094</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.001790642738342285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.002655386924743652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.002495646476745605</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.007531285285949707</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.005354642868041992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.005524158477783203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.006863236427307129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.007567048072814941</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.003514528274536133</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.005280971527099609</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.008574485778808594</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.009108424186706543</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.001998066902160645</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.00770258903503418</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.008942246437072754</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.004013299942016602</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.006599783897399902</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.002728939056396484</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008450627326965332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.00806725025177002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.009935379028320312</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.001123309135437012</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01523423194885254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.003882646560668945</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.02189207077026367</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.00377357006072998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.003278136253356934</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.01453399658203125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.003144145011901855</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.003370046615600586</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.005634307861328125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.005341410636901855</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.009418129920959473</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.002452373504638672</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.00844573974609375</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.01065981388092041</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.00541985034942627</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.007751584053039551</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.007155418395996094</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.002372384071350098</v>
       </c>
     </row>
   </sheetData>
@@ -8949,12 +15989,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.02235686779022217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.02077674865722656</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.02952301502227783</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02111184597015381</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.01478254795074463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03327226638793945</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.02878344058990479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.0303351879119873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.04349827766418457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.04812192916870117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.02718627452850342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03519594669342041</v>
       </c>
     </row>
   </sheetData>
